--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4587"/>
+  <dimension ref="A1:F4588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92152,10 +92152,10 @@
         <v>46230</v>
       </c>
       <c r="B4587" t="n">
-        <v>25.47</v>
+        <v>25.46999931335449</v>
       </c>
       <c r="C4587" t="n">
-        <v>25.53</v>
+        <v>25.53000068664551</v>
       </c>
       <c r="D4587" t="n">
         <v>25</v>
@@ -92165,6 +92165,26 @@
       </c>
       <c r="F4587" t="n">
         <v>4002300</v>
+      </c>
+    </row>
+    <row r="4588">
+      <c r="A4588" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B4588" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="C4588" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="D4588" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="E4588" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="F4588" t="n">
+        <v>1268500</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -92172,7 +92172,7 @@
         <v>46231</v>
       </c>
       <c r="B4588" t="n">
-        <v>25.69</v>
+        <v>25.86</v>
       </c>
       <c r="C4588" t="n">
         <v>26.12</v>
@@ -92184,7 +92184,7 @@
         <v>26.03</v>
       </c>
       <c r="F4588" t="n">
-        <v>1268500</v>
+        <v>3951000</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -92172,7 +92172,7 @@
         <v>46231</v>
       </c>
       <c r="B4588" t="n">
-        <v>25.86</v>
+        <v>25.85</v>
       </c>
       <c r="C4588" t="n">
         <v>26.12</v>
@@ -92184,7 +92184,7 @@
         <v>26.03</v>
       </c>
       <c r="F4588" t="n">
-        <v>3951000</v>
+        <v>8990600</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -92172,16 +92172,16 @@
         <v>46231</v>
       </c>
       <c r="B4588" t="n">
-        <v>25.85</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="C4588" t="n">
-        <v>26.12</v>
+        <v>26.1200008392334</v>
       </c>
       <c r="D4588" t="n">
-        <v>25.61</v>
+        <v>25.61000061035156</v>
       </c>
       <c r="E4588" t="n">
-        <v>26.03</v>
+        <v>26.03000068664551</v>
       </c>
       <c r="F4588" t="n">
         <v>8990600</v>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4588"/>
+  <dimension ref="A1:F4589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92187,6 +92187,26 @@
         <v>8990600</v>
       </c>
     </row>
+    <row r="4589">
+      <c r="A4589" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B4589" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="C4589" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="D4589" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="E4589" t="n">
+        <v>25.68</v>
+      </c>
+      <c r="F4589" t="n">
+        <v>7233100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -92192,7 +92192,7 @@
         <v>46232</v>
       </c>
       <c r="B4589" t="n">
-        <v>25.81</v>
+        <v>25.87</v>
       </c>
       <c r="C4589" t="n">
         <v>26.37</v>
@@ -92204,7 +92204,7 @@
         <v>25.68</v>
       </c>
       <c r="F4589" t="n">
-        <v>7233100</v>
+        <v>10386600</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4589"/>
+  <dimension ref="A1:F4590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92192,19 +92192,39 @@
         <v>46232</v>
       </c>
       <c r="B4589" t="n">
-        <v>25.87</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="C4589" t="n">
-        <v>26.37</v>
+        <v>26.3700008392334</v>
       </c>
       <c r="D4589" t="n">
-        <v>25.61</v>
+        <v>25.61000061035156</v>
       </c>
       <c r="E4589" t="n">
-        <v>25.68</v>
+        <v>25.68000030517578</v>
       </c>
       <c r="F4589" t="n">
         <v>10386600</v>
+      </c>
+    </row>
+    <row r="4590">
+      <c r="A4590" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B4590" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="C4590" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="D4590" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="E4590" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F4590" t="n">
+        <v>7244900</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4590"/>
+  <dimension ref="A1:F4591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92212,19 +92212,39 @@
         <v>46233</v>
       </c>
       <c r="B4590" t="n">
-        <v>26.15</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="C4590" t="n">
-        <v>26.33</v>
+        <v>26.32999992370605</v>
       </c>
       <c r="D4590" t="n">
-        <v>25.89</v>
+        <v>25.88999938964844</v>
       </c>
       <c r="E4590" t="n">
-        <v>26.1</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="F4590" t="n">
         <v>7244900</v>
+      </c>
+    </row>
+    <row r="4591">
+      <c r="A4591" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B4591" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="C4591" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="D4591" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="E4591" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="F4591" t="n">
+        <v>7686800</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4591"/>
+  <dimension ref="A1:F4592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92232,19 +92232,39 @@
         <v>46234</v>
       </c>
       <c r="B4591" t="n">
-        <v>26.31</v>
+        <v>26.30999946594238</v>
       </c>
       <c r="C4591" t="n">
-        <v>26.54</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="D4591" t="n">
-        <v>25.97</v>
+        <v>25.96999931335449</v>
       </c>
       <c r="E4591" t="n">
-        <v>26.54</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="F4591" t="n">
         <v>7686800</v>
+      </c>
+    </row>
+    <row r="4592">
+      <c r="A4592" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B4592" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="C4592" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="D4592" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E4592" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="F4592" t="n">
+        <v>7476500</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -92229,42 +92229,42 @@
     </row>
     <row r="4591">
       <c r="A4591" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B4591" t="n">
-        <v>26.30999946594238</v>
+        <v>26.75</v>
       </c>
       <c r="C4591" t="n">
-        <v>26.54000091552734</v>
+        <v>26.92000007629395</v>
       </c>
       <c r="D4591" t="n">
-        <v>25.96999931335449</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="E4591" t="n">
-        <v>26.54000091552734</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="F4591" t="n">
-        <v>7686800</v>
+        <v>7476500</v>
       </c>
     </row>
     <row r="4592">
       <c r="A4592" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B4592" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="C4592" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="D4592" t="n">
         <v>26.75</v>
       </c>
-      <c r="C4592" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="D4592" t="n">
-        <v>26.2</v>
-      </c>
       <c r="E4592" t="n">
-        <v>26.65</v>
+        <v>27.3</v>
       </c>
       <c r="F4592" t="n">
-        <v>7476500</v>
+        <v>5295200</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4592"/>
+  <dimension ref="A1:F4594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92229,42 +92229,82 @@
     </row>
     <row r="4591">
       <c r="A4591" s="1" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B4591" t="n">
-        <v>26.75</v>
+        <v>26.30999946594238</v>
       </c>
       <c r="C4591" t="n">
-        <v>26.92000007629395</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="D4591" t="n">
-        <v>26.20000076293945</v>
+        <v>25.96999931335449</v>
       </c>
       <c r="E4591" t="n">
-        <v>26.64999961853027</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="F4591" t="n">
-        <v>7476500</v>
+        <v>7686800</v>
       </c>
     </row>
     <row r="4592">
       <c r="A4592" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B4592" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="C4592" t="n">
+        <v>26.92000007629395</v>
+      </c>
+      <c r="D4592" t="n">
+        <v>26.20000076293945</v>
+      </c>
+      <c r="E4592" t="n">
+        <v>26.64999961853027</v>
+      </c>
+      <c r="F4592" t="n">
+        <v>7476500</v>
+      </c>
+    </row>
+    <row r="4593">
+      <c r="A4593" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="B4592" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="C4592" t="n">
-        <v>27.53</v>
-      </c>
-      <c r="D4592" t="n">
+      <c r="B4593" t="n">
+        <v>27.15999984741211</v>
+      </c>
+      <c r="C4593" t="n">
+        <v>27.53000068664551</v>
+      </c>
+      <c r="D4593" t="n">
         <v>26.75</v>
       </c>
-      <c r="E4592" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="F4592" t="n">
+      <c r="E4593" t="n">
+        <v>27.29999923706055</v>
+      </c>
+      <c r="F4593" t="n">
         <v>5295200</v>
+      </c>
+    </row>
+    <row r="4594">
+      <c r="A4594" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B4594" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="C4594" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="D4594" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="E4594" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="F4594" t="n">
+        <v>4842600</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4594"/>
+  <dimension ref="A1:F4595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92292,19 +92292,39 @@
         <v>46239</v>
       </c>
       <c r="B4594" t="n">
-        <v>26.98</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="C4594" t="n">
-        <v>27.67</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="D4594" t="n">
-        <v>26.98</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="E4594" t="n">
-        <v>27.35</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="F4594" t="n">
         <v>4842600</v>
+      </c>
+    </row>
+    <row r="4595">
+      <c r="A4595" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B4595" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C4595" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="D4595" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="E4595" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="F4595" t="n">
+        <v>5412100</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -92229,102 +92229,102 @@
     </row>
     <row r="4591">
       <c r="A4591" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B4591" t="n">
-        <v>26.30999946594238</v>
+        <v>26.75</v>
       </c>
       <c r="C4591" t="n">
-        <v>26.54000091552734</v>
+        <v>26.92000007629395</v>
       </c>
       <c r="D4591" t="n">
-        <v>25.96999931335449</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="E4591" t="n">
-        <v>26.54000091552734</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="F4591" t="n">
-        <v>7686800</v>
+        <v>7476500</v>
       </c>
     </row>
     <row r="4592">
       <c r="A4592" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B4592" t="n">
+        <v>27.15999984741211</v>
+      </c>
+      <c r="C4592" t="n">
+        <v>27.53000068664551</v>
+      </c>
+      <c r="D4592" t="n">
         <v>26.75</v>
       </c>
-      <c r="C4592" t="n">
-        <v>26.92000007629395</v>
-      </c>
-      <c r="D4592" t="n">
-        <v>26.20000076293945</v>
-      </c>
       <c r="E4592" t="n">
-        <v>26.64999961853027</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="F4592" t="n">
-        <v>7476500</v>
+        <v>5295200</v>
       </c>
     </row>
     <row r="4593">
       <c r="A4593" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B4593" t="n">
-        <v>27.15999984741211</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="C4593" t="n">
-        <v>27.53000068664551</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="D4593" t="n">
-        <v>26.75</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="E4593" t="n">
-        <v>27.29999923706055</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="F4593" t="n">
-        <v>5295200</v>
+        <v>4842600</v>
       </c>
     </row>
     <row r="4594">
       <c r="A4594" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B4594" t="n">
-        <v>26.97999954223633</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="C4594" t="n">
-        <v>27.67000007629395</v>
+        <v>26.86000061035156</v>
       </c>
       <c r="D4594" t="n">
-        <v>26.97999954223633</v>
+        <v>26.36000061035156</v>
       </c>
       <c r="E4594" t="n">
-        <v>27.35000038146973</v>
+        <v>26.75</v>
       </c>
       <c r="F4594" t="n">
-        <v>4842600</v>
+        <v>5412100</v>
       </c>
     </row>
     <row r="4595">
       <c r="A4595" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B4595" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="C4595" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="D4595" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="E4595" t="n">
         <v>26.6</v>
       </c>
-      <c r="C4595" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="D4595" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="E4595" t="n">
-        <v>26.75</v>
-      </c>
       <c r="F4595" t="n">
-        <v>5412100</v>
+        <v>5534600</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4595"/>
+  <dimension ref="A1:F4597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92229,102 +92229,142 @@
     </row>
     <row r="4591">
       <c r="A4591" s="1" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B4591" t="n">
-        <v>26.75</v>
+        <v>26.30999946594238</v>
       </c>
       <c r="C4591" t="n">
-        <v>26.92000007629395</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="D4591" t="n">
-        <v>26.20000076293945</v>
+        <v>25.96999931335449</v>
       </c>
       <c r="E4591" t="n">
-        <v>26.64999961853027</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="F4591" t="n">
-        <v>7476500</v>
+        <v>7686800</v>
       </c>
     </row>
     <row r="4592">
       <c r="A4592" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B4592" t="n">
-        <v>27.15999984741211</v>
+        <v>26.75</v>
       </c>
       <c r="C4592" t="n">
-        <v>27.53000068664551</v>
+        <v>26.92000007629395</v>
       </c>
       <c r="D4592" t="n">
-        <v>26.75</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="E4592" t="n">
-        <v>27.29999923706055</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="F4592" t="n">
-        <v>5295200</v>
+        <v>7476500</v>
       </c>
     </row>
     <row r="4593">
       <c r="A4593" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B4593" t="n">
-        <v>26.97999954223633</v>
+        <v>27.15999984741211</v>
       </c>
       <c r="C4593" t="n">
-        <v>27.67000007629395</v>
+        <v>27.53000068664551</v>
       </c>
       <c r="D4593" t="n">
-        <v>26.97999954223633</v>
+        <v>26.75</v>
       </c>
       <c r="E4593" t="n">
-        <v>27.35000038146973</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="F4593" t="n">
-        <v>4842600</v>
+        <v>5295200</v>
       </c>
     </row>
     <row r="4594">
       <c r="A4594" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B4594" t="n">
-        <v>26.60000038146973</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="C4594" t="n">
-        <v>26.86000061035156</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="D4594" t="n">
-        <v>26.36000061035156</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="E4594" t="n">
-        <v>26.75</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="F4594" t="n">
-        <v>5412100</v>
+        <v>4842600</v>
       </c>
     </row>
     <row r="4595">
       <c r="A4595" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B4595" t="n">
+        <v>26.60000038146973</v>
+      </c>
+      <c r="C4595" t="n">
+        <v>26.86000061035156</v>
+      </c>
+      <c r="D4595" t="n">
+        <v>26.36000061035156</v>
+      </c>
+      <c r="E4595" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="F4595" t="n">
+        <v>5412100</v>
+      </c>
+    </row>
+    <row r="4596">
+      <c r="A4596" s="1" t="n">
         <v>46241</v>
       </c>
-      <c r="B4595" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="C4595" t="n">
-        <v>26.69</v>
-      </c>
-      <c r="D4595" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="E4595" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="F4595" t="n">
+      <c r="B4596" t="n">
+        <v>26.18000030517578</v>
+      </c>
+      <c r="C4596" t="n">
+        <v>26.69000053405762</v>
+      </c>
+      <c r="D4596" t="n">
+        <v>25.95000076293945</v>
+      </c>
+      <c r="E4596" t="n">
+        <v>26.60000038146973</v>
+      </c>
+      <c r="F4596" t="n">
         <v>5534600</v>
+      </c>
+    </row>
+    <row r="4597">
+      <c r="A4597" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B4597" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="C4597" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="D4597" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E4597" t="n">
+        <v>25.96</v>
+      </c>
+      <c r="F4597" t="n">
+        <v>11408000</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4597"/>
+  <dimension ref="A1:F4598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92352,19 +92352,39 @@
         <v>46244</v>
       </c>
       <c r="B4597" t="n">
-        <v>25.32</v>
+        <v>25.31999969482422</v>
       </c>
       <c r="C4597" t="n">
-        <v>26.15</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="D4597" t="n">
-        <v>25.3</v>
+        <v>25.29999923706055</v>
       </c>
       <c r="E4597" t="n">
-        <v>25.96</v>
+        <v>25.95999908447266</v>
       </c>
       <c r="F4597" t="n">
         <v>11408000</v>
+      </c>
+    </row>
+    <row r="4598">
+      <c r="A4598" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B4598" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="C4598" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="D4598" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E4598" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F4598" t="n">
+        <v>12371700</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4598"/>
+  <dimension ref="A1:F4597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92229,162 +92229,142 @@
     </row>
     <row r="4591">
       <c r="A4591" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B4591" t="n">
-        <v>26.30999946594238</v>
+        <v>26.75</v>
       </c>
       <c r="C4591" t="n">
-        <v>26.54000091552734</v>
+        <v>26.92000007629395</v>
       </c>
       <c r="D4591" t="n">
-        <v>25.96999931335449</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="E4591" t="n">
-        <v>26.54000091552734</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="F4591" t="n">
-        <v>7686800</v>
+        <v>7476500</v>
       </c>
     </row>
     <row r="4592">
       <c r="A4592" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B4592" t="n">
+        <v>27.15999984741211</v>
+      </c>
+      <c r="C4592" t="n">
+        <v>27.53000068664551</v>
+      </c>
+      <c r="D4592" t="n">
         <v>26.75</v>
       </c>
-      <c r="C4592" t="n">
-        <v>26.92000007629395</v>
-      </c>
-      <c r="D4592" t="n">
-        <v>26.20000076293945</v>
-      </c>
       <c r="E4592" t="n">
-        <v>26.64999961853027</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="F4592" t="n">
-        <v>7476500</v>
+        <v>5295200</v>
       </c>
     </row>
     <row r="4593">
       <c r="A4593" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B4593" t="n">
-        <v>27.15999984741211</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="C4593" t="n">
-        <v>27.53000068664551</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="D4593" t="n">
-        <v>26.75</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="E4593" t="n">
-        <v>27.29999923706055</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="F4593" t="n">
-        <v>5295200</v>
+        <v>4842600</v>
       </c>
     </row>
     <row r="4594">
       <c r="A4594" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B4594" t="n">
-        <v>26.97999954223633</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="C4594" t="n">
-        <v>27.67000007629395</v>
+        <v>26.86000061035156</v>
       </c>
       <c r="D4594" t="n">
-        <v>26.97999954223633</v>
+        <v>26.36000061035156</v>
       </c>
       <c r="E4594" t="n">
-        <v>27.35000038146973</v>
+        <v>26.75</v>
       </c>
       <c r="F4594" t="n">
-        <v>4842600</v>
+        <v>5412100</v>
       </c>
     </row>
     <row r="4595">
       <c r="A4595" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B4595" t="n">
+        <v>26.18000030517578</v>
+      </c>
+      <c r="C4595" t="n">
+        <v>26.69000053405762</v>
+      </c>
+      <c r="D4595" t="n">
+        <v>25.95000076293945</v>
+      </c>
+      <c r="E4595" t="n">
         <v>26.60000038146973</v>
       </c>
-      <c r="C4595" t="n">
-        <v>26.86000061035156</v>
-      </c>
-      <c r="D4595" t="n">
-        <v>26.36000061035156</v>
-      </c>
-      <c r="E4595" t="n">
-        <v>26.75</v>
-      </c>
       <c r="F4595" t="n">
-        <v>5412100</v>
+        <v>5534600</v>
       </c>
     </row>
     <row r="4596">
       <c r="A4596" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B4596" t="n">
-        <v>26.18000030517578</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="C4596" t="n">
-        <v>26.69000053405762</v>
+        <v>25.38999938964844</v>
       </c>
       <c r="D4596" t="n">
-        <v>25.95000076293945</v>
+        <v>24.5</v>
       </c>
       <c r="E4596" t="n">
-        <v>26.60000038146973</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="F4596" t="n">
-        <v>5534600</v>
+        <v>12371700</v>
       </c>
     </row>
     <row r="4597">
       <c r="A4597" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B4597" t="n">
-        <v>25.31999969482422</v>
+        <v>24.11</v>
       </c>
       <c r="C4597" t="n">
-        <v>26.14999961853027</v>
+        <v>24.64</v>
       </c>
       <c r="D4597" t="n">
-        <v>25.29999923706055</v>
+        <v>23.99</v>
       </c>
       <c r="E4597" t="n">
-        <v>25.95999908447266</v>
+        <v>24.54</v>
       </c>
       <c r="F4597" t="n">
-        <v>11408000</v>
-      </c>
-    </row>
-    <row r="4598">
-      <c r="A4598" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B4598" t="n">
-        <v>24.55</v>
-      </c>
-      <c r="C4598" t="n">
-        <v>25.39</v>
-      </c>
-      <c r="D4598" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E4598" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="F4598" t="n">
-        <v>12371700</v>
+        <v>16842400</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4597"/>
+  <dimension ref="A1:F4598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92352,19 +92352,39 @@
         <v>46246</v>
       </c>
       <c r="B4597" t="n">
-        <v>24.11</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="C4597" t="n">
-        <v>24.64</v>
+        <v>24.63999938964844</v>
       </c>
       <c r="D4597" t="n">
-        <v>23.99</v>
+        <v>23.98999977111816</v>
       </c>
       <c r="E4597" t="n">
-        <v>24.54</v>
+        <v>24.54000091552734</v>
       </c>
       <c r="F4597" t="n">
         <v>16842400</v>
+      </c>
+    </row>
+    <row r="4598">
+      <c r="A4598" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B4598" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="C4598" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="D4598" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="E4598" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="F4598" t="n">
+        <v>9052700</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4598"/>
+  <dimension ref="A1:F4599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92049,282 +92049,282 @@
     </row>
     <row r="4582">
       <c r="A4582" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B4582" t="n">
-        <v>25.64999961853027</v>
+        <v>25.42000007629395</v>
       </c>
       <c r="C4582" t="n">
-        <v>25.84000015258789</v>
+        <v>25.65999984741211</v>
       </c>
       <c r="D4582" t="n">
-        <v>25.47999954223633</v>
+        <v>25.1200008392334</v>
       </c>
       <c r="E4582" t="n">
-        <v>25.68000030517578</v>
+        <v>25.60000038146973</v>
       </c>
       <c r="F4582" t="n">
-        <v>6955700</v>
+        <v>4083900</v>
       </c>
     </row>
     <row r="4583">
       <c r="A4583" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B4583" t="n">
-        <v>25.42000007629395</v>
+        <v>25.96999931335449</v>
       </c>
       <c r="C4583" t="n">
-        <v>25.65999984741211</v>
+        <v>26.07999992370605</v>
       </c>
       <c r="D4583" t="n">
-        <v>25.1200008392334</v>
+        <v>25.31999969482422</v>
       </c>
       <c r="E4583" t="n">
-        <v>25.60000038146973</v>
+        <v>25.45999908447266</v>
       </c>
       <c r="F4583" t="n">
-        <v>4083900</v>
+        <v>5927100</v>
       </c>
     </row>
     <row r="4584">
       <c r="A4584" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B4584" t="n">
-        <v>25.96999931335449</v>
+        <v>25.70000076293945</v>
       </c>
       <c r="C4584" t="n">
-        <v>26.07999992370605</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="D4584" t="n">
-        <v>25.31999969482422</v>
+        <v>25.45000076293945</v>
       </c>
       <c r="E4584" t="n">
-        <v>25.45999908447266</v>
+        <v>25.75</v>
       </c>
       <c r="F4584" t="n">
-        <v>5927100</v>
+        <v>3291700</v>
       </c>
     </row>
     <row r="4585">
       <c r="A4585" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B4585" t="n">
-        <v>25.70000076293945</v>
+        <v>24.89999961853027</v>
       </c>
       <c r="C4585" t="n">
-        <v>25.79999923706055</v>
+        <v>25.57999992370605</v>
       </c>
       <c r="D4585" t="n">
-        <v>25.45000076293945</v>
+        <v>24.8700008392334</v>
       </c>
       <c r="E4585" t="n">
-        <v>25.75</v>
+        <v>25.46999931335449</v>
       </c>
       <c r="F4585" t="n">
-        <v>3291700</v>
+        <v>4495600</v>
       </c>
     </row>
     <row r="4586">
       <c r="A4586" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B4586" t="n">
-        <v>24.89999961853027</v>
+        <v>25.46999931335449</v>
       </c>
       <c r="C4586" t="n">
-        <v>25.57999992370605</v>
+        <v>25.53000068664551</v>
       </c>
       <c r="D4586" t="n">
-        <v>24.8700008392334</v>
+        <v>25</v>
       </c>
       <c r="E4586" t="n">
-        <v>25.46999931335449</v>
+        <v>25</v>
       </c>
       <c r="F4586" t="n">
-        <v>4495600</v>
+        <v>4002300</v>
       </c>
     </row>
     <row r="4587">
       <c r="A4587" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B4587" t="n">
-        <v>25.46999931335449</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="C4587" t="n">
-        <v>25.53000068664551</v>
+        <v>26.1200008392334</v>
       </c>
       <c r="D4587" t="n">
-        <v>25</v>
+        <v>25.61000061035156</v>
       </c>
       <c r="E4587" t="n">
-        <v>25</v>
+        <v>26.03000068664551</v>
       </c>
       <c r="F4587" t="n">
-        <v>4002300</v>
+        <v>8990600</v>
       </c>
     </row>
     <row r="4588">
       <c r="A4588" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B4588" t="n">
-        <v>25.85000038146973</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="C4588" t="n">
-        <v>26.1200008392334</v>
+        <v>26.3700008392334</v>
       </c>
       <c r="D4588" t="n">
         <v>25.61000061035156</v>
       </c>
       <c r="E4588" t="n">
-        <v>26.03000068664551</v>
+        <v>25.68000030517578</v>
       </c>
       <c r="F4588" t="n">
-        <v>8990600</v>
+        <v>10386600</v>
       </c>
     </row>
     <row r="4589">
       <c r="A4589" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B4589" t="n">
-        <v>25.8700008392334</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="C4589" t="n">
-        <v>26.3700008392334</v>
+        <v>26.32999992370605</v>
       </c>
       <c r="D4589" t="n">
-        <v>25.61000061035156</v>
+        <v>25.88999938964844</v>
       </c>
       <c r="E4589" t="n">
-        <v>25.68000030517578</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="F4589" t="n">
-        <v>10386600</v>
+        <v>7244900</v>
       </c>
     </row>
     <row r="4590">
       <c r="A4590" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B4590" t="n">
-        <v>26.14999961853027</v>
+        <v>26.75</v>
       </c>
       <c r="C4590" t="n">
-        <v>26.32999992370605</v>
+        <v>26.92000007629395</v>
       </c>
       <c r="D4590" t="n">
-        <v>25.88999938964844</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="E4590" t="n">
-        <v>26.10000038146973</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="F4590" t="n">
-        <v>7244900</v>
+        <v>7476500</v>
       </c>
     </row>
     <row r="4591">
       <c r="A4591" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B4591" t="n">
+        <v>27.15999984741211</v>
+      </c>
+      <c r="C4591" t="n">
+        <v>27.53000068664551</v>
+      </c>
+      <c r="D4591" t="n">
         <v>26.75</v>
       </c>
-      <c r="C4591" t="n">
-        <v>26.92000007629395</v>
-      </c>
-      <c r="D4591" t="n">
-        <v>26.20000076293945</v>
-      </c>
       <c r="E4591" t="n">
-        <v>26.64999961853027</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="F4591" t="n">
-        <v>7476500</v>
+        <v>5295200</v>
       </c>
     </row>
     <row r="4592">
       <c r="A4592" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B4592" t="n">
-        <v>27.15999984741211</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="C4592" t="n">
-        <v>27.53000068664551</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="D4592" t="n">
-        <v>26.75</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="E4592" t="n">
-        <v>27.29999923706055</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="F4592" t="n">
-        <v>5295200</v>
+        <v>4842600</v>
       </c>
     </row>
     <row r="4593">
       <c r="A4593" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B4593" t="n">
-        <v>26.97999954223633</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="C4593" t="n">
-        <v>27.67000007629395</v>
+        <v>26.86000061035156</v>
       </c>
       <c r="D4593" t="n">
-        <v>26.97999954223633</v>
+        <v>26.36000061035156</v>
       </c>
       <c r="E4593" t="n">
-        <v>27.35000038146973</v>
+        <v>26.75</v>
       </c>
       <c r="F4593" t="n">
-        <v>4842600</v>
+        <v>5412100</v>
       </c>
     </row>
     <row r="4594">
       <c r="A4594" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B4594" t="n">
+        <v>26.18000030517578</v>
+      </c>
+      <c r="C4594" t="n">
+        <v>26.69000053405762</v>
+      </c>
+      <c r="D4594" t="n">
+        <v>25.95000076293945</v>
+      </c>
+      <c r="E4594" t="n">
         <v>26.60000038146973</v>
       </c>
-      <c r="C4594" t="n">
-        <v>26.86000061035156</v>
-      </c>
-      <c r="D4594" t="n">
-        <v>26.36000061035156</v>
-      </c>
-      <c r="E4594" t="n">
-        <v>26.75</v>
-      </c>
       <c r="F4594" t="n">
-        <v>5412100</v>
+        <v>5534600</v>
       </c>
     </row>
     <row r="4595">
       <c r="A4595" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B4595" t="n">
-        <v>26.18000030517578</v>
+        <v>25.31999969482422</v>
       </c>
       <c r="C4595" t="n">
-        <v>26.69000053405762</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="D4595" t="n">
-        <v>25.95000076293945</v>
+        <v>25.29999923706055</v>
       </c>
       <c r="E4595" t="n">
-        <v>26.60000038146973</v>
+        <v>25.95999908447266</v>
       </c>
       <c r="F4595" t="n">
-        <v>5534600</v>
+        <v>11408000</v>
       </c>
     </row>
     <row r="4596">
@@ -92372,19 +92372,39 @@
         <v>46247</v>
       </c>
       <c r="B4598" t="n">
-        <v>24.34</v>
+        <v>24.34000015258789</v>
       </c>
       <c r="C4598" t="n">
-        <v>24.72</v>
+        <v>24.71999931335449</v>
       </c>
       <c r="D4598" t="n">
-        <v>24.03</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="E4598" t="n">
-        <v>24.11</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="F4598" t="n">
         <v>9052700</v>
+      </c>
+    </row>
+    <row r="4599">
+      <c r="A4599" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B4599" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="C4599" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="D4599" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E4599" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F4599" t="n">
+        <v>13652000</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4599"/>
+  <dimension ref="A1:F4602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92049,362 +92049,422 @@
     </row>
     <row r="4582">
       <c r="A4582" s="1" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B4582" t="n">
-        <v>25.42000007629395</v>
+        <v>25.64999961853027</v>
       </c>
       <c r="C4582" t="n">
-        <v>25.65999984741211</v>
+        <v>25.84000015258789</v>
       </c>
       <c r="D4582" t="n">
-        <v>25.1200008392334</v>
+        <v>25.47999954223633</v>
       </c>
       <c r="E4582" t="n">
-        <v>25.60000038146973</v>
+        <v>25.68000030517578</v>
       </c>
       <c r="F4582" t="n">
-        <v>4083900</v>
+        <v>6955700</v>
       </c>
     </row>
     <row r="4583">
       <c r="A4583" s="1" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B4583" t="n">
-        <v>25.96999931335449</v>
+        <v>25.42000007629395</v>
       </c>
       <c r="C4583" t="n">
-        <v>26.07999992370605</v>
+        <v>25.65999984741211</v>
       </c>
       <c r="D4583" t="n">
-        <v>25.31999969482422</v>
+        <v>25.1200008392334</v>
       </c>
       <c r="E4583" t="n">
-        <v>25.45999908447266</v>
+        <v>25.60000038146973</v>
       </c>
       <c r="F4583" t="n">
-        <v>5927100</v>
+        <v>4083900</v>
       </c>
     </row>
     <row r="4584">
       <c r="A4584" s="1" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B4584" t="n">
-        <v>25.70000076293945</v>
+        <v>25.96999931335449</v>
       </c>
       <c r="C4584" t="n">
-        <v>25.79999923706055</v>
+        <v>26.07999992370605</v>
       </c>
       <c r="D4584" t="n">
-        <v>25.45000076293945</v>
+        <v>25.31999969482422</v>
       </c>
       <c r="E4584" t="n">
-        <v>25.75</v>
+        <v>25.45999908447266</v>
       </c>
       <c r="F4584" t="n">
-        <v>3291700</v>
+        <v>5927100</v>
       </c>
     </row>
     <row r="4585">
       <c r="A4585" s="1" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B4585" t="n">
-        <v>24.89999961853027</v>
+        <v>25.70000076293945</v>
       </c>
       <c r="C4585" t="n">
-        <v>25.57999992370605</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="D4585" t="n">
-        <v>24.8700008392334</v>
+        <v>25.45000076293945</v>
       </c>
       <c r="E4585" t="n">
-        <v>25.46999931335449</v>
+        <v>25.75</v>
       </c>
       <c r="F4585" t="n">
-        <v>4495600</v>
+        <v>3291700</v>
       </c>
     </row>
     <row r="4586">
       <c r="A4586" s="1" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B4586" t="n">
+        <v>24.89999961853027</v>
+      </c>
+      <c r="C4586" t="n">
+        <v>25.57999992370605</v>
+      </c>
+      <c r="D4586" t="n">
+        <v>24.8700008392334</v>
+      </c>
+      <c r="E4586" t="n">
         <v>25.46999931335449</v>
       </c>
-      <c r="C4586" t="n">
-        <v>25.53000068664551</v>
-      </c>
-      <c r="D4586" t="n">
-        <v>25</v>
-      </c>
-      <c r="E4586" t="n">
-        <v>25</v>
-      </c>
       <c r="F4586" t="n">
-        <v>4002300</v>
+        <v>4495600</v>
       </c>
     </row>
     <row r="4587">
       <c r="A4587" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B4587" t="n">
-        <v>25.85000038146973</v>
+        <v>25.46999931335449</v>
       </c>
       <c r="C4587" t="n">
-        <v>26.1200008392334</v>
+        <v>25.53000068664551</v>
       </c>
       <c r="D4587" t="n">
-        <v>25.61000061035156</v>
+        <v>25</v>
       </c>
       <c r="E4587" t="n">
-        <v>26.03000068664551</v>
+        <v>25</v>
       </c>
       <c r="F4587" t="n">
-        <v>8990600</v>
+        <v>4002300</v>
       </c>
     </row>
     <row r="4588">
       <c r="A4588" s="1" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B4588" t="n">
-        <v>25.8700008392334</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="C4588" t="n">
-        <v>26.3700008392334</v>
+        <v>26.1200008392334</v>
       </c>
       <c r="D4588" t="n">
         <v>25.61000061035156</v>
       </c>
       <c r="E4588" t="n">
-        <v>25.68000030517578</v>
+        <v>26.03000068664551</v>
       </c>
       <c r="F4588" t="n">
-        <v>10386600</v>
+        <v>8990600</v>
       </c>
     </row>
     <row r="4589">
       <c r="A4589" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B4589" t="n">
-        <v>26.14999961853027</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="C4589" t="n">
-        <v>26.32999992370605</v>
+        <v>26.3700008392334</v>
       </c>
       <c r="D4589" t="n">
-        <v>25.88999938964844</v>
+        <v>25.61000061035156</v>
       </c>
       <c r="E4589" t="n">
-        <v>26.10000038146973</v>
+        <v>25.68000030517578</v>
       </c>
       <c r="F4589" t="n">
-        <v>7244900</v>
+        <v>10386600</v>
       </c>
     </row>
     <row r="4590">
       <c r="A4590" s="1" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B4590" t="n">
-        <v>26.75</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="C4590" t="n">
-        <v>26.92000007629395</v>
+        <v>26.32999992370605</v>
       </c>
       <c r="D4590" t="n">
-        <v>26.20000076293945</v>
+        <v>25.88999938964844</v>
       </c>
       <c r="E4590" t="n">
-        <v>26.64999961853027</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="F4590" t="n">
-        <v>7476500</v>
+        <v>7244900</v>
       </c>
     </row>
     <row r="4591">
       <c r="A4591" s="1" t="n">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="B4591" t="n">
-        <v>27.15999984741211</v>
+        <v>26.30999946594238</v>
       </c>
       <c r="C4591" t="n">
-        <v>27.53000068664551</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="D4591" t="n">
-        <v>26.75</v>
+        <v>25.96999931335449</v>
       </c>
       <c r="E4591" t="n">
-        <v>27.29999923706055</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="F4591" t="n">
-        <v>5295200</v>
+        <v>7686800</v>
       </c>
     </row>
     <row r="4592">
       <c r="A4592" s="1" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="B4592" t="n">
-        <v>26.97999954223633</v>
+        <v>26.75</v>
       </c>
       <c r="C4592" t="n">
-        <v>27.67000007629395</v>
+        <v>26.92000007629395</v>
       </c>
       <c r="D4592" t="n">
-        <v>26.97999954223633</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="E4592" t="n">
-        <v>27.35000038146973</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="F4592" t="n">
-        <v>4842600</v>
+        <v>7476500</v>
       </c>
     </row>
     <row r="4593">
       <c r="A4593" s="1" t="n">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="B4593" t="n">
-        <v>26.60000038146973</v>
+        <v>27.15999984741211</v>
       </c>
       <c r="C4593" t="n">
-        <v>26.86000061035156</v>
+        <v>27.53000068664551</v>
       </c>
       <c r="D4593" t="n">
-        <v>26.36000061035156</v>
+        <v>26.75</v>
       </c>
       <c r="E4593" t="n">
-        <v>26.75</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="F4593" t="n">
-        <v>5412100</v>
+        <v>5295200</v>
       </c>
     </row>
     <row r="4594">
       <c r="A4594" s="1" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="B4594" t="n">
-        <v>26.18000030517578</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="C4594" t="n">
-        <v>26.69000053405762</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="D4594" t="n">
-        <v>25.95000076293945</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="E4594" t="n">
-        <v>26.60000038146973</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="F4594" t="n">
-        <v>5534600</v>
+        <v>4842600</v>
       </c>
     </row>
     <row r="4595">
       <c r="A4595" s="1" t="n">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="B4595" t="n">
-        <v>25.31999969482422</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="C4595" t="n">
-        <v>26.14999961853027</v>
+        <v>26.86000061035156</v>
       </c>
       <c r="D4595" t="n">
-        <v>25.29999923706055</v>
+        <v>26.36000061035156</v>
       </c>
       <c r="E4595" t="n">
-        <v>25.95999908447266</v>
+        <v>26.75</v>
       </c>
       <c r="F4595" t="n">
-        <v>11408000</v>
+        <v>5412100</v>
       </c>
     </row>
     <row r="4596">
       <c r="A4596" s="1" t="n">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="B4596" t="n">
-        <v>24.54999923706055</v>
+        <v>26.18000030517578</v>
       </c>
       <c r="C4596" t="n">
-        <v>25.38999938964844</v>
+        <v>26.69000053405762</v>
       </c>
       <c r="D4596" t="n">
-        <v>24.5</v>
+        <v>25.95000076293945</v>
       </c>
       <c r="E4596" t="n">
-        <v>25.20000076293945</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="F4596" t="n">
-        <v>12371700</v>
+        <v>5534600</v>
       </c>
     </row>
     <row r="4597">
       <c r="A4597" s="1" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B4597" t="n">
-        <v>24.11000061035156</v>
+        <v>25.31999969482422</v>
       </c>
       <c r="C4597" t="n">
-        <v>24.63999938964844</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="D4597" t="n">
-        <v>23.98999977111816</v>
+        <v>25.29999923706055</v>
       </c>
       <c r="E4597" t="n">
-        <v>24.54000091552734</v>
+        <v>25.95999908447266</v>
       </c>
       <c r="F4597" t="n">
-        <v>16842400</v>
+        <v>11408000</v>
       </c>
     </row>
     <row r="4598">
       <c r="A4598" s="1" t="n">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="B4598" t="n">
-        <v>24.34000015258789</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="C4598" t="n">
-        <v>24.71999931335449</v>
+        <v>25.38999938964844</v>
       </c>
       <c r="D4598" t="n">
-        <v>24.03000068664551</v>
+        <v>24.5</v>
       </c>
       <c r="E4598" t="n">
-        <v>24.11000061035156</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="F4598" t="n">
-        <v>9052700</v>
+        <v>12371700</v>
       </c>
     </row>
     <row r="4599">
       <c r="A4599" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B4599" t="n">
+        <v>24.11000061035156</v>
+      </c>
+      <c r="C4599" t="n">
+        <v>24.63999938964844</v>
+      </c>
+      <c r="D4599" t="n">
+        <v>23.98999977111816</v>
+      </c>
+      <c r="E4599" t="n">
+        <v>24.54000091552734</v>
+      </c>
+      <c r="F4599" t="n">
+        <v>16842400</v>
+      </c>
+    </row>
+    <row r="4600">
+      <c r="A4600" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B4600" t="n">
+        <v>24.34000015258789</v>
+      </c>
+      <c r="C4600" t="n">
+        <v>24.71999931335449</v>
+      </c>
+      <c r="D4600" t="n">
+        <v>24.03000068664551</v>
+      </c>
+      <c r="E4600" t="n">
+        <v>24.11000061035156</v>
+      </c>
+      <c r="F4600" t="n">
+        <v>9052700</v>
+      </c>
+    </row>
+    <row r="4601">
+      <c r="A4601" s="1" t="n">
         <v>46248</v>
       </c>
-      <c r="B4599" t="n">
-        <v>24.45</v>
-      </c>
-      <c r="C4599" t="n">
-        <v>24.61</v>
-      </c>
-      <c r="D4599" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="E4599" t="n">
+      <c r="B4601" t="n">
+        <v>24.45000076293945</v>
+      </c>
+      <c r="C4601" t="n">
+        <v>24.61000061035156</v>
+      </c>
+      <c r="D4601" t="n">
+        <v>23.64999961853027</v>
+      </c>
+      <c r="E4601" t="n">
+        <v>24.20000076293945</v>
+      </c>
+      <c r="F4601" t="n">
+        <v>13652000</v>
+      </c>
+    </row>
+    <row r="4602">
+      <c r="A4602" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B4602" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="C4602" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="D4602" t="n">
         <v>24.2</v>
       </c>
-      <c r="F4599" t="n">
-        <v>13652000</v>
+      <c r="E4602" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="F4602" t="n">
+        <v>12423700</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4602"/>
+  <dimension ref="A1:F4601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92229,242 +92229,222 @@
     </row>
     <row r="4591">
       <c r="A4591" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B4591" t="n">
-        <v>26.30999946594238</v>
+        <v>26.75</v>
       </c>
       <c r="C4591" t="n">
-        <v>26.54000091552734</v>
+        <v>26.92000007629395</v>
       </c>
       <c r="D4591" t="n">
-        <v>25.96999931335449</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="E4591" t="n">
-        <v>26.54000091552734</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="F4591" t="n">
-        <v>7686800</v>
+        <v>7476500</v>
       </c>
     </row>
     <row r="4592">
       <c r="A4592" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B4592" t="n">
+        <v>27.15999984741211</v>
+      </c>
+      <c r="C4592" t="n">
+        <v>27.53000068664551</v>
+      </c>
+      <c r="D4592" t="n">
         <v>26.75</v>
       </c>
-      <c r="C4592" t="n">
-        <v>26.92000007629395</v>
-      </c>
-      <c r="D4592" t="n">
-        <v>26.20000076293945</v>
-      </c>
       <c r="E4592" t="n">
-        <v>26.64999961853027</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="F4592" t="n">
-        <v>7476500</v>
+        <v>5295200</v>
       </c>
     </row>
     <row r="4593">
       <c r="A4593" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B4593" t="n">
-        <v>27.15999984741211</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="C4593" t="n">
-        <v>27.53000068664551</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="D4593" t="n">
-        <v>26.75</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="E4593" t="n">
-        <v>27.29999923706055</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="F4593" t="n">
-        <v>5295200</v>
+        <v>4842600</v>
       </c>
     </row>
     <row r="4594">
       <c r="A4594" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B4594" t="n">
-        <v>26.97999954223633</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="C4594" t="n">
-        <v>27.67000007629395</v>
+        <v>26.86000061035156</v>
       </c>
       <c r="D4594" t="n">
-        <v>26.97999954223633</v>
+        <v>26.36000061035156</v>
       </c>
       <c r="E4594" t="n">
-        <v>27.35000038146973</v>
+        <v>26.75</v>
       </c>
       <c r="F4594" t="n">
-        <v>4842600</v>
+        <v>5412100</v>
       </c>
     </row>
     <row r="4595">
       <c r="A4595" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B4595" t="n">
+        <v>26.18000030517578</v>
+      </c>
+      <c r="C4595" t="n">
+        <v>26.69000053405762</v>
+      </c>
+      <c r="D4595" t="n">
+        <v>25.95000076293945</v>
+      </c>
+      <c r="E4595" t="n">
         <v>26.60000038146973</v>
       </c>
-      <c r="C4595" t="n">
-        <v>26.86000061035156</v>
-      </c>
-      <c r="D4595" t="n">
-        <v>26.36000061035156</v>
-      </c>
-      <c r="E4595" t="n">
-        <v>26.75</v>
-      </c>
       <c r="F4595" t="n">
-        <v>5412100</v>
+        <v>5534600</v>
       </c>
     </row>
     <row r="4596">
       <c r="A4596" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B4596" t="n">
-        <v>26.18000030517578</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="C4596" t="n">
-        <v>26.69000053405762</v>
+        <v>25.38999938964844</v>
       </c>
       <c r="D4596" t="n">
-        <v>25.95000076293945</v>
+        <v>24.5</v>
       </c>
       <c r="E4596" t="n">
-        <v>26.60000038146973</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="F4596" t="n">
-        <v>5534600</v>
+        <v>12371700</v>
       </c>
     </row>
     <row r="4597">
       <c r="A4597" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B4597" t="n">
-        <v>25.31999969482422</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="C4597" t="n">
-        <v>26.14999961853027</v>
+        <v>24.63999938964844</v>
       </c>
       <c r="D4597" t="n">
-        <v>25.29999923706055</v>
+        <v>23.98999977111816</v>
       </c>
       <c r="E4597" t="n">
-        <v>25.95999908447266</v>
+        <v>24.54000091552734</v>
       </c>
       <c r="F4597" t="n">
-        <v>11408000</v>
+        <v>16842400</v>
       </c>
     </row>
     <row r="4598">
       <c r="A4598" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B4598" t="n">
-        <v>24.54999923706055</v>
+        <v>24.34000015258789</v>
       </c>
       <c r="C4598" t="n">
-        <v>25.38999938964844</v>
+        <v>24.71999931335449</v>
       </c>
       <c r="D4598" t="n">
-        <v>24.5</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="E4598" t="n">
-        <v>25.20000076293945</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="F4598" t="n">
-        <v>12371700</v>
+        <v>9052700</v>
       </c>
     </row>
     <row r="4599">
       <c r="A4599" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B4599" t="n">
-        <v>24.11000061035156</v>
+        <v>24.45000076293945</v>
       </c>
       <c r="C4599" t="n">
-        <v>24.63999938964844</v>
+        <v>24.61000061035156</v>
       </c>
       <c r="D4599" t="n">
-        <v>23.98999977111816</v>
+        <v>23.64999961853027</v>
       </c>
       <c r="E4599" t="n">
-        <v>24.54000091552734</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="F4599" t="n">
-        <v>16842400</v>
+        <v>13652000</v>
       </c>
     </row>
     <row r="4600">
       <c r="A4600" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B4600" t="n">
-        <v>24.34000015258789</v>
+        <v>24.53000068664551</v>
       </c>
       <c r="C4600" t="n">
-        <v>24.71999931335449</v>
+        <v>24.8700008392334</v>
       </c>
       <c r="D4600" t="n">
-        <v>24.03000068664551</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="E4600" t="n">
-        <v>24.11000061035156</v>
+        <v>24.3799991607666</v>
       </c>
       <c r="F4600" t="n">
-        <v>9052700</v>
+        <v>12423700</v>
       </c>
     </row>
     <row r="4601">
       <c r="A4601" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B4601" t="n">
-        <v>24.45000076293945</v>
+        <v>24.65</v>
       </c>
       <c r="C4601" t="n">
-        <v>24.61000061035156</v>
+        <v>24.91</v>
       </c>
       <c r="D4601" t="n">
-        <v>23.64999961853027</v>
+        <v>24.35</v>
       </c>
       <c r="E4601" t="n">
-        <v>24.20000076293945</v>
+        <v>24.48</v>
       </c>
       <c r="F4601" t="n">
-        <v>13652000</v>
-      </c>
-    </row>
-    <row r="4602">
-      <c r="A4602" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="B4602" t="n">
-        <v>24.53</v>
-      </c>
-      <c r="C4602" t="n">
-        <v>24.87</v>
-      </c>
-      <c r="D4602" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E4602" t="n">
-        <v>24.38</v>
-      </c>
-      <c r="F4602" t="n">
-        <v>12423700</v>
+        <v>6850200</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4601"/>
+  <dimension ref="A1:F4602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92049,282 +92049,282 @@
     </row>
     <row r="4582">
       <c r="A4582" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B4582" t="n">
-        <v>25.64999961853027</v>
+        <v>25.42000007629395</v>
       </c>
       <c r="C4582" t="n">
-        <v>25.84000015258789</v>
+        <v>25.65999984741211</v>
       </c>
       <c r="D4582" t="n">
-        <v>25.47999954223633</v>
+        <v>25.1200008392334</v>
       </c>
       <c r="E4582" t="n">
-        <v>25.68000030517578</v>
+        <v>25.60000038146973</v>
       </c>
       <c r="F4582" t="n">
-        <v>6955700</v>
+        <v>4083900</v>
       </c>
     </row>
     <row r="4583">
       <c r="A4583" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B4583" t="n">
-        <v>25.42000007629395</v>
+        <v>25.96999931335449</v>
       </c>
       <c r="C4583" t="n">
-        <v>25.65999984741211</v>
+        <v>26.07999992370605</v>
       </c>
       <c r="D4583" t="n">
-        <v>25.1200008392334</v>
+        <v>25.31999969482422</v>
       </c>
       <c r="E4583" t="n">
-        <v>25.60000038146973</v>
+        <v>25.45999908447266</v>
       </c>
       <c r="F4583" t="n">
-        <v>4083900</v>
+        <v>5927100</v>
       </c>
     </row>
     <row r="4584">
       <c r="A4584" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B4584" t="n">
-        <v>25.96999931335449</v>
+        <v>25.70000076293945</v>
       </c>
       <c r="C4584" t="n">
-        <v>26.07999992370605</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="D4584" t="n">
-        <v>25.31999969482422</v>
+        <v>25.45000076293945</v>
       </c>
       <c r="E4584" t="n">
-        <v>25.45999908447266</v>
+        <v>25.75</v>
       </c>
       <c r="F4584" t="n">
-        <v>5927100</v>
+        <v>3291700</v>
       </c>
     </row>
     <row r="4585">
       <c r="A4585" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B4585" t="n">
-        <v>25.70000076293945</v>
+        <v>24.89999961853027</v>
       </c>
       <c r="C4585" t="n">
-        <v>25.79999923706055</v>
+        <v>25.57999992370605</v>
       </c>
       <c r="D4585" t="n">
-        <v>25.45000076293945</v>
+        <v>24.8700008392334</v>
       </c>
       <c r="E4585" t="n">
-        <v>25.75</v>
+        <v>25.46999931335449</v>
       </c>
       <c r="F4585" t="n">
-        <v>3291700</v>
+        <v>4495600</v>
       </c>
     </row>
     <row r="4586">
       <c r="A4586" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B4586" t="n">
-        <v>24.89999961853027</v>
+        <v>25.46999931335449</v>
       </c>
       <c r="C4586" t="n">
-        <v>25.57999992370605</v>
+        <v>25.53000068664551</v>
       </c>
       <c r="D4586" t="n">
-        <v>24.8700008392334</v>
+        <v>25</v>
       </c>
       <c r="E4586" t="n">
-        <v>25.46999931335449</v>
+        <v>25</v>
       </c>
       <c r="F4586" t="n">
-        <v>4495600</v>
+        <v>4002300</v>
       </c>
     </row>
     <row r="4587">
       <c r="A4587" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B4587" t="n">
-        <v>25.46999931335449</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="C4587" t="n">
-        <v>25.53000068664551</v>
+        <v>26.1200008392334</v>
       </c>
       <c r="D4587" t="n">
-        <v>25</v>
+        <v>25.61000061035156</v>
       </c>
       <c r="E4587" t="n">
-        <v>25</v>
+        <v>26.03000068664551</v>
       </c>
       <c r="F4587" t="n">
-        <v>4002300</v>
+        <v>8990600</v>
       </c>
     </row>
     <row r="4588">
       <c r="A4588" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B4588" t="n">
-        <v>25.85000038146973</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="C4588" t="n">
-        <v>26.1200008392334</v>
+        <v>26.3700008392334</v>
       </c>
       <c r="D4588" t="n">
         <v>25.61000061035156</v>
       </c>
       <c r="E4588" t="n">
-        <v>26.03000068664551</v>
+        <v>25.68000030517578</v>
       </c>
       <c r="F4588" t="n">
-        <v>8990600</v>
+        <v>10386600</v>
       </c>
     </row>
     <row r="4589">
       <c r="A4589" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B4589" t="n">
-        <v>25.8700008392334</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="C4589" t="n">
-        <v>26.3700008392334</v>
+        <v>26.32999992370605</v>
       </c>
       <c r="D4589" t="n">
-        <v>25.61000061035156</v>
+        <v>25.88999938964844</v>
       </c>
       <c r="E4589" t="n">
-        <v>25.68000030517578</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="F4589" t="n">
-        <v>10386600</v>
+        <v>7244900</v>
       </c>
     </row>
     <row r="4590">
       <c r="A4590" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B4590" t="n">
-        <v>26.14999961853027</v>
+        <v>26.75</v>
       </c>
       <c r="C4590" t="n">
-        <v>26.32999992370605</v>
+        <v>26.92000007629395</v>
       </c>
       <c r="D4590" t="n">
-        <v>25.88999938964844</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="E4590" t="n">
-        <v>26.10000038146973</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="F4590" t="n">
-        <v>7244900</v>
+        <v>7476500</v>
       </c>
     </row>
     <row r="4591">
       <c r="A4591" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B4591" t="n">
+        <v>27.15999984741211</v>
+      </c>
+      <c r="C4591" t="n">
+        <v>27.53000068664551</v>
+      </c>
+      <c r="D4591" t="n">
         <v>26.75</v>
       </c>
-      <c r="C4591" t="n">
-        <v>26.92000007629395</v>
-      </c>
-      <c r="D4591" t="n">
-        <v>26.20000076293945</v>
-      </c>
       <c r="E4591" t="n">
-        <v>26.64999961853027</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="F4591" t="n">
-        <v>7476500</v>
+        <v>5295200</v>
       </c>
     </row>
     <row r="4592">
       <c r="A4592" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B4592" t="n">
-        <v>27.15999984741211</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="C4592" t="n">
-        <v>27.53000068664551</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="D4592" t="n">
-        <v>26.75</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="E4592" t="n">
-        <v>27.29999923706055</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="F4592" t="n">
-        <v>5295200</v>
+        <v>4842600</v>
       </c>
     </row>
     <row r="4593">
       <c r="A4593" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B4593" t="n">
-        <v>26.97999954223633</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="C4593" t="n">
-        <v>27.67000007629395</v>
+        <v>26.86000061035156</v>
       </c>
       <c r="D4593" t="n">
-        <v>26.97999954223633</v>
+        <v>26.36000061035156</v>
       </c>
       <c r="E4593" t="n">
-        <v>27.35000038146973</v>
+        <v>26.75</v>
       </c>
       <c r="F4593" t="n">
-        <v>4842600</v>
+        <v>5412100</v>
       </c>
     </row>
     <row r="4594">
       <c r="A4594" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B4594" t="n">
+        <v>26.18000030517578</v>
+      </c>
+      <c r="C4594" t="n">
+        <v>26.69000053405762</v>
+      </c>
+      <c r="D4594" t="n">
+        <v>25.95000076293945</v>
+      </c>
+      <c r="E4594" t="n">
         <v>26.60000038146973</v>
       </c>
-      <c r="C4594" t="n">
-        <v>26.86000061035156</v>
-      </c>
-      <c r="D4594" t="n">
-        <v>26.36000061035156</v>
-      </c>
-      <c r="E4594" t="n">
-        <v>26.75</v>
-      </c>
       <c r="F4594" t="n">
-        <v>5412100</v>
+        <v>5534600</v>
       </c>
     </row>
     <row r="4595">
       <c r="A4595" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B4595" t="n">
-        <v>26.18000030517578</v>
+        <v>25.31999969482422</v>
       </c>
       <c r="C4595" t="n">
-        <v>26.69000053405762</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="D4595" t="n">
-        <v>25.95000076293945</v>
+        <v>25.29999923706055</v>
       </c>
       <c r="E4595" t="n">
-        <v>26.60000038146973</v>
+        <v>25.95999908447266</v>
       </c>
       <c r="F4595" t="n">
-        <v>5534600</v>
+        <v>11408000</v>
       </c>
     </row>
     <row r="4596">
@@ -92432,19 +92432,39 @@
         <v>46252</v>
       </c>
       <c r="B4601" t="n">
-        <v>24.65</v>
+        <v>24.64999961853027</v>
       </c>
       <c r="C4601" t="n">
-        <v>24.91</v>
+        <v>24.90999984741211</v>
       </c>
       <c r="D4601" t="n">
-        <v>24.35</v>
+        <v>24.35000038146973</v>
       </c>
       <c r="E4601" t="n">
-        <v>24.48</v>
+        <v>24.47999954223633</v>
       </c>
       <c r="F4601" t="n">
         <v>6850200</v>
+      </c>
+    </row>
+    <row r="4602">
+      <c r="A4602" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B4602" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="C4602" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="D4602" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="E4602" t="n">
+        <v>25.13</v>
+      </c>
+      <c r="F4602" t="n">
+        <v>13455000</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4602"/>
+  <dimension ref="A1:F4603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92049,282 +92049,282 @@
     </row>
     <row r="4582">
       <c r="A4582" s="1" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B4582" t="n">
-        <v>25.42000007629395</v>
+        <v>25.64999961853027</v>
       </c>
       <c r="C4582" t="n">
-        <v>25.65999984741211</v>
+        <v>25.84000015258789</v>
       </c>
       <c r="D4582" t="n">
-        <v>25.1200008392334</v>
+        <v>25.47999954223633</v>
       </c>
       <c r="E4582" t="n">
-        <v>25.60000038146973</v>
+        <v>25.68000030517578</v>
       </c>
       <c r="F4582" t="n">
-        <v>4083900</v>
+        <v>6955700</v>
       </c>
     </row>
     <row r="4583">
       <c r="A4583" s="1" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B4583" t="n">
-        <v>25.96999931335449</v>
+        <v>25.42000007629395</v>
       </c>
       <c r="C4583" t="n">
-        <v>26.07999992370605</v>
+        <v>25.65999984741211</v>
       </c>
       <c r="D4583" t="n">
-        <v>25.31999969482422</v>
+        <v>25.1200008392334</v>
       </c>
       <c r="E4583" t="n">
-        <v>25.45999908447266</v>
+        <v>25.60000038146973</v>
       </c>
       <c r="F4583" t="n">
-        <v>5927100</v>
+        <v>4083900</v>
       </c>
     </row>
     <row r="4584">
       <c r="A4584" s="1" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B4584" t="n">
-        <v>25.70000076293945</v>
+        <v>25.96999931335449</v>
       </c>
       <c r="C4584" t="n">
-        <v>25.79999923706055</v>
+        <v>26.07999992370605</v>
       </c>
       <c r="D4584" t="n">
-        <v>25.45000076293945</v>
+        <v>25.31999969482422</v>
       </c>
       <c r="E4584" t="n">
-        <v>25.75</v>
+        <v>25.45999908447266</v>
       </c>
       <c r="F4584" t="n">
-        <v>3291700</v>
+        <v>5927100</v>
       </c>
     </row>
     <row r="4585">
       <c r="A4585" s="1" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B4585" t="n">
-        <v>24.89999961853027</v>
+        <v>25.70000076293945</v>
       </c>
       <c r="C4585" t="n">
-        <v>25.57999992370605</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="D4585" t="n">
-        <v>24.8700008392334</v>
+        <v>25.45000076293945</v>
       </c>
       <c r="E4585" t="n">
-        <v>25.46999931335449</v>
+        <v>25.75</v>
       </c>
       <c r="F4585" t="n">
-        <v>4495600</v>
+        <v>3291700</v>
       </c>
     </row>
     <row r="4586">
       <c r="A4586" s="1" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B4586" t="n">
+        <v>24.89999961853027</v>
+      </c>
+      <c r="C4586" t="n">
+        <v>25.57999992370605</v>
+      </c>
+      <c r="D4586" t="n">
+        <v>24.8700008392334</v>
+      </c>
+      <c r="E4586" t="n">
         <v>25.46999931335449</v>
       </c>
-      <c r="C4586" t="n">
-        <v>25.53000068664551</v>
-      </c>
-      <c r="D4586" t="n">
-        <v>25</v>
-      </c>
-      <c r="E4586" t="n">
-        <v>25</v>
-      </c>
       <c r="F4586" t="n">
-        <v>4002300</v>
+        <v>4495600</v>
       </c>
     </row>
     <row r="4587">
       <c r="A4587" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B4587" t="n">
-        <v>25.85000038146973</v>
+        <v>25.46999931335449</v>
       </c>
       <c r="C4587" t="n">
-        <v>26.1200008392334</v>
+        <v>25.53000068664551</v>
       </c>
       <c r="D4587" t="n">
-        <v>25.61000061035156</v>
+        <v>25</v>
       </c>
       <c r="E4587" t="n">
-        <v>26.03000068664551</v>
+        <v>25</v>
       </c>
       <c r="F4587" t="n">
-        <v>8990600</v>
+        <v>4002300</v>
       </c>
     </row>
     <row r="4588">
       <c r="A4588" s="1" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B4588" t="n">
-        <v>25.8700008392334</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="C4588" t="n">
-        <v>26.3700008392334</v>
+        <v>26.1200008392334</v>
       </c>
       <c r="D4588" t="n">
         <v>25.61000061035156</v>
       </c>
       <c r="E4588" t="n">
-        <v>25.68000030517578</v>
+        <v>26.03000068664551</v>
       </c>
       <c r="F4588" t="n">
-        <v>10386600</v>
+        <v>8990600</v>
       </c>
     </row>
     <row r="4589">
       <c r="A4589" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B4589" t="n">
-        <v>26.14999961853027</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="C4589" t="n">
-        <v>26.32999992370605</v>
+        <v>26.3700008392334</v>
       </c>
       <c r="D4589" t="n">
-        <v>25.88999938964844</v>
+        <v>25.61000061035156</v>
       </c>
       <c r="E4589" t="n">
-        <v>26.10000038146973</v>
+        <v>25.68000030517578</v>
       </c>
       <c r="F4589" t="n">
-        <v>7244900</v>
+        <v>10386600</v>
       </c>
     </row>
     <row r="4590">
       <c r="A4590" s="1" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B4590" t="n">
-        <v>26.75</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="C4590" t="n">
-        <v>26.92000007629395</v>
+        <v>26.32999992370605</v>
       </c>
       <c r="D4590" t="n">
-        <v>26.20000076293945</v>
+        <v>25.88999938964844</v>
       </c>
       <c r="E4590" t="n">
-        <v>26.64999961853027</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="F4590" t="n">
-        <v>7476500</v>
+        <v>7244900</v>
       </c>
     </row>
     <row r="4591">
       <c r="A4591" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B4591" t="n">
-        <v>27.15999984741211</v>
+        <v>26.75</v>
       </c>
       <c r="C4591" t="n">
-        <v>27.53000068664551</v>
+        <v>26.92000007629395</v>
       </c>
       <c r="D4591" t="n">
-        <v>26.75</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="E4591" t="n">
-        <v>27.29999923706055</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="F4591" t="n">
-        <v>5295200</v>
+        <v>7476500</v>
       </c>
     </row>
     <row r="4592">
       <c r="A4592" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B4592" t="n">
-        <v>26.97999954223633</v>
+        <v>27.15999984741211</v>
       </c>
       <c r="C4592" t="n">
-        <v>27.67000007629395</v>
+        <v>27.53000068664551</v>
       </c>
       <c r="D4592" t="n">
-        <v>26.97999954223633</v>
+        <v>26.75</v>
       </c>
       <c r="E4592" t="n">
-        <v>27.35000038146973</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="F4592" t="n">
-        <v>4842600</v>
+        <v>5295200</v>
       </c>
     </row>
     <row r="4593">
       <c r="A4593" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B4593" t="n">
-        <v>26.60000038146973</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="C4593" t="n">
-        <v>26.86000061035156</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="D4593" t="n">
-        <v>26.36000061035156</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="E4593" t="n">
-        <v>26.75</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="F4593" t="n">
-        <v>5412100</v>
+        <v>4842600</v>
       </c>
     </row>
     <row r="4594">
       <c r="A4594" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B4594" t="n">
-        <v>26.18000030517578</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="C4594" t="n">
-        <v>26.69000053405762</v>
+        <v>26.86000061035156</v>
       </c>
       <c r="D4594" t="n">
-        <v>25.95000076293945</v>
+        <v>26.36000061035156</v>
       </c>
       <c r="E4594" t="n">
-        <v>26.60000038146973</v>
+        <v>26.75</v>
       </c>
       <c r="F4594" t="n">
-        <v>5534600</v>
+        <v>5412100</v>
       </c>
     </row>
     <row r="4595">
       <c r="A4595" s="1" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B4595" t="n">
-        <v>25.31999969482422</v>
+        <v>26.18000030517578</v>
       </c>
       <c r="C4595" t="n">
-        <v>26.14999961853027</v>
+        <v>26.69000053405762</v>
       </c>
       <c r="D4595" t="n">
-        <v>25.29999923706055</v>
+        <v>25.95000076293945</v>
       </c>
       <c r="E4595" t="n">
-        <v>25.95999908447266</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="F4595" t="n">
-        <v>11408000</v>
+        <v>5534600</v>
       </c>
     </row>
     <row r="4596">
@@ -92452,19 +92452,39 @@
         <v>46253</v>
       </c>
       <c r="B4602" t="n">
-        <v>25.1</v>
+        <v>25.10000038146973</v>
       </c>
       <c r="C4602" t="n">
-        <v>25.36</v>
+        <v>25.36000061035156</v>
       </c>
       <c r="D4602" t="n">
-        <v>24.77</v>
+        <v>24.77000045776367</v>
       </c>
       <c r="E4602" t="n">
-        <v>25.13</v>
+        <v>25.1299991607666</v>
       </c>
       <c r="F4602" t="n">
         <v>13455000</v>
+      </c>
+    </row>
+    <row r="4603">
+      <c r="A4603" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B4603" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="C4603" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="D4603" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="E4603" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F4603" t="n">
+        <v>7580500</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4603"/>
+  <dimension ref="A1:F4605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92229,262 +92229,302 @@
     </row>
     <row r="4591">
       <c r="A4591" s="1" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B4591" t="n">
-        <v>26.75</v>
+        <v>26.30999946594238</v>
       </c>
       <c r="C4591" t="n">
-        <v>26.92000007629395</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="D4591" t="n">
-        <v>26.20000076293945</v>
+        <v>25.96999931335449</v>
       </c>
       <c r="E4591" t="n">
-        <v>26.64999961853027</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="F4591" t="n">
-        <v>7476500</v>
+        <v>7686800</v>
       </c>
     </row>
     <row r="4592">
       <c r="A4592" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B4592" t="n">
-        <v>27.15999984741211</v>
+        <v>26.75</v>
       </c>
       <c r="C4592" t="n">
-        <v>27.53000068664551</v>
+        <v>26.92000007629395</v>
       </c>
       <c r="D4592" t="n">
-        <v>26.75</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="E4592" t="n">
-        <v>27.29999923706055</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="F4592" t="n">
-        <v>5295200</v>
+        <v>7476500</v>
       </c>
     </row>
     <row r="4593">
       <c r="A4593" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B4593" t="n">
-        <v>26.97999954223633</v>
+        <v>27.15999984741211</v>
       </c>
       <c r="C4593" t="n">
-        <v>27.67000007629395</v>
+        <v>27.53000068664551</v>
       </c>
       <c r="D4593" t="n">
-        <v>26.97999954223633</v>
+        <v>26.75</v>
       </c>
       <c r="E4593" t="n">
-        <v>27.35000038146973</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="F4593" t="n">
-        <v>4842600</v>
+        <v>5295200</v>
       </c>
     </row>
     <row r="4594">
       <c r="A4594" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B4594" t="n">
-        <v>26.60000038146973</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="C4594" t="n">
-        <v>26.86000061035156</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="D4594" t="n">
-        <v>26.36000061035156</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="E4594" t="n">
-        <v>26.75</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="F4594" t="n">
-        <v>5412100</v>
+        <v>4842600</v>
       </c>
     </row>
     <row r="4595">
       <c r="A4595" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B4595" t="n">
-        <v>26.18000030517578</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="C4595" t="n">
-        <v>26.69000053405762</v>
+        <v>26.86000061035156</v>
       </c>
       <c r="D4595" t="n">
-        <v>25.95000076293945</v>
+        <v>26.36000061035156</v>
       </c>
       <c r="E4595" t="n">
-        <v>26.60000038146973</v>
+        <v>26.75</v>
       </c>
       <c r="F4595" t="n">
-        <v>5534600</v>
+        <v>5412100</v>
       </c>
     </row>
     <row r="4596">
       <c r="A4596" s="1" t="n">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="B4596" t="n">
-        <v>24.54999923706055</v>
+        <v>26.18000030517578</v>
       </c>
       <c r="C4596" t="n">
-        <v>25.38999938964844</v>
+        <v>26.69000053405762</v>
       </c>
       <c r="D4596" t="n">
-        <v>24.5</v>
+        <v>25.95000076293945</v>
       </c>
       <c r="E4596" t="n">
-        <v>25.20000076293945</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="F4596" t="n">
-        <v>12371700</v>
+        <v>5534600</v>
       </c>
     </row>
     <row r="4597">
       <c r="A4597" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B4597" t="n">
-        <v>24.11000061035156</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="C4597" t="n">
-        <v>24.63999938964844</v>
+        <v>25.38999938964844</v>
       </c>
       <c r="D4597" t="n">
-        <v>23.98999977111816</v>
+        <v>24.5</v>
       </c>
       <c r="E4597" t="n">
-        <v>24.54000091552734</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="F4597" t="n">
-        <v>16842400</v>
+        <v>12371700</v>
       </c>
     </row>
     <row r="4598">
       <c r="A4598" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B4598" t="n">
-        <v>24.34000015258789</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="C4598" t="n">
-        <v>24.71999931335449</v>
+        <v>24.63999938964844</v>
       </c>
       <c r="D4598" t="n">
-        <v>24.03000068664551</v>
+        <v>23.98999977111816</v>
       </c>
       <c r="E4598" t="n">
-        <v>24.11000061035156</v>
+        <v>24.54000091552734</v>
       </c>
       <c r="F4598" t="n">
-        <v>9052700</v>
+        <v>16842400</v>
       </c>
     </row>
     <row r="4599">
       <c r="A4599" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B4599" t="n">
-        <v>24.45000076293945</v>
+        <v>24.34000015258789</v>
       </c>
       <c r="C4599" t="n">
-        <v>24.61000061035156</v>
+        <v>24.71999931335449</v>
       </c>
       <c r="D4599" t="n">
-        <v>23.64999961853027</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="E4599" t="n">
-        <v>24.20000076293945</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="F4599" t="n">
-        <v>13652000</v>
+        <v>9052700</v>
       </c>
     </row>
     <row r="4600">
       <c r="A4600" s="1" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B4600" t="n">
-        <v>24.53000068664551</v>
+        <v>24.45000076293945</v>
       </c>
       <c r="C4600" t="n">
-        <v>24.8700008392334</v>
+        <v>24.61000061035156</v>
       </c>
       <c r="D4600" t="n">
+        <v>23.64999961853027</v>
+      </c>
+      <c r="E4600" t="n">
         <v>24.20000076293945</v>
       </c>
-      <c r="E4600" t="n">
-        <v>24.3799991607666</v>
-      </c>
       <c r="F4600" t="n">
-        <v>12423700</v>
+        <v>13652000</v>
       </c>
     </row>
     <row r="4601">
       <c r="A4601" s="1" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B4601" t="n">
-        <v>24.64999961853027</v>
+        <v>24.53000068664551</v>
       </c>
       <c r="C4601" t="n">
-        <v>24.90999984741211</v>
+        <v>24.8700008392334</v>
       </c>
       <c r="D4601" t="n">
-        <v>24.35000038146973</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="E4601" t="n">
-        <v>24.47999954223633</v>
+        <v>24.3799991607666</v>
       </c>
       <c r="F4601" t="n">
-        <v>6850200</v>
+        <v>12423700</v>
       </c>
     </row>
     <row r="4602">
       <c r="A4602" s="1" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B4602" t="n">
-        <v>25.10000038146973</v>
+        <v>24.64999961853027</v>
       </c>
       <c r="C4602" t="n">
-        <v>25.36000061035156</v>
+        <v>24.90999984741211</v>
       </c>
       <c r="D4602" t="n">
-        <v>24.77000045776367</v>
+        <v>24.35000038146973</v>
       </c>
       <c r="E4602" t="n">
-        <v>25.1299991607666</v>
+        <v>24.47999954223633</v>
       </c>
       <c r="F4602" t="n">
-        <v>13455000</v>
+        <v>6850200</v>
       </c>
     </row>
     <row r="4603">
       <c r="A4603" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B4603" t="n">
+        <v>25.10000038146973</v>
+      </c>
+      <c r="C4603" t="n">
+        <v>25.36000061035156</v>
+      </c>
+      <c r="D4603" t="n">
+        <v>24.77000045776367</v>
+      </c>
+      <c r="E4603" t="n">
+        <v>25.1299991607666</v>
+      </c>
+      <c r="F4603" t="n">
+        <v>13455000</v>
+      </c>
+    </row>
+    <row r="4604">
+      <c r="A4604" s="1" t="n">
         <v>46254</v>
       </c>
-      <c r="B4603" t="n">
-        <v>24.92</v>
-      </c>
-      <c r="C4603" t="n">
-        <v>25.38</v>
-      </c>
-      <c r="D4603" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="E4603" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="F4603" t="n">
+      <c r="B4604" t="n">
+        <v>24.92000007629395</v>
+      </c>
+      <c r="C4604" t="n">
+        <v>25.3799991607666</v>
+      </c>
+      <c r="D4604" t="n">
+        <v>24.8799991607666</v>
+      </c>
+      <c r="E4604" t="n">
+        <v>24.89999961853027</v>
+      </c>
+      <c r="F4604" t="n">
         <v>7580500</v>
+      </c>
+    </row>
+    <row r="4605">
+      <c r="A4605" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B4605" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="C4605" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="D4605" t="n">
+        <v>24.93</v>
+      </c>
+      <c r="E4605" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="F4605" t="n">
+        <v>27481200</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4605"/>
+  <dimension ref="A1:F4607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92349,182 +92349,222 @@
     </row>
     <row r="4597">
       <c r="A4597" s="1" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B4597" t="n">
-        <v>24.54999923706055</v>
+        <v>25.31999969482422</v>
       </c>
       <c r="C4597" t="n">
-        <v>25.38999938964844</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="D4597" t="n">
-        <v>24.5</v>
+        <v>25.29999923706055</v>
       </c>
       <c r="E4597" t="n">
-        <v>25.20000076293945</v>
+        <v>25.95999908447266</v>
       </c>
       <c r="F4597" t="n">
-        <v>12371700</v>
+        <v>11408000</v>
       </c>
     </row>
     <row r="4598">
       <c r="A4598" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B4598" t="n">
-        <v>24.11000061035156</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="C4598" t="n">
-        <v>24.63999938964844</v>
+        <v>25.38999938964844</v>
       </c>
       <c r="D4598" t="n">
-        <v>23.98999977111816</v>
+        <v>24.5</v>
       </c>
       <c r="E4598" t="n">
-        <v>24.54000091552734</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="F4598" t="n">
-        <v>16842400</v>
+        <v>12371700</v>
       </c>
     </row>
     <row r="4599">
       <c r="A4599" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B4599" t="n">
-        <v>24.34000015258789</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="C4599" t="n">
-        <v>24.71999931335449</v>
+        <v>24.63999938964844</v>
       </c>
       <c r="D4599" t="n">
-        <v>24.03000068664551</v>
+        <v>23.98999977111816</v>
       </c>
       <c r="E4599" t="n">
-        <v>24.11000061035156</v>
+        <v>24.54000091552734</v>
       </c>
       <c r="F4599" t="n">
-        <v>9052700</v>
+        <v>16842400</v>
       </c>
     </row>
     <row r="4600">
       <c r="A4600" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B4600" t="n">
-        <v>24.45000076293945</v>
+        <v>24.34000015258789</v>
       </c>
       <c r="C4600" t="n">
-        <v>24.61000061035156</v>
+        <v>24.71999931335449</v>
       </c>
       <c r="D4600" t="n">
-        <v>23.64999961853027</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="E4600" t="n">
-        <v>24.20000076293945</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="F4600" t="n">
-        <v>13652000</v>
+        <v>9052700</v>
       </c>
     </row>
     <row r="4601">
       <c r="A4601" s="1" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B4601" t="n">
-        <v>24.53000068664551</v>
+        <v>24.45000076293945</v>
       </c>
       <c r="C4601" t="n">
-        <v>24.8700008392334</v>
+        <v>24.61000061035156</v>
       </c>
       <c r="D4601" t="n">
+        <v>23.64999961853027</v>
+      </c>
+      <c r="E4601" t="n">
         <v>24.20000076293945</v>
       </c>
-      <c r="E4601" t="n">
-        <v>24.3799991607666</v>
-      </c>
       <c r="F4601" t="n">
-        <v>12423700</v>
+        <v>13652000</v>
       </c>
     </row>
     <row r="4602">
       <c r="A4602" s="1" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B4602" t="n">
-        <v>24.64999961853027</v>
+        <v>24.53000068664551</v>
       </c>
       <c r="C4602" t="n">
-        <v>24.90999984741211</v>
+        <v>24.8700008392334</v>
       </c>
       <c r="D4602" t="n">
-        <v>24.35000038146973</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="E4602" t="n">
-        <v>24.47999954223633</v>
+        <v>24.3799991607666</v>
       </c>
       <c r="F4602" t="n">
-        <v>6850200</v>
+        <v>12423700</v>
       </c>
     </row>
     <row r="4603">
       <c r="A4603" s="1" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B4603" t="n">
-        <v>25.10000038146973</v>
+        <v>24.64999961853027</v>
       </c>
       <c r="C4603" t="n">
-        <v>25.36000061035156</v>
+        <v>24.90999984741211</v>
       </c>
       <c r="D4603" t="n">
-        <v>24.77000045776367</v>
+        <v>24.35000038146973</v>
       </c>
       <c r="E4603" t="n">
-        <v>25.1299991607666</v>
+        <v>24.47999954223633</v>
       </c>
       <c r="F4603" t="n">
-        <v>13455000</v>
+        <v>6850200</v>
       </c>
     </row>
     <row r="4604">
       <c r="A4604" s="1" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B4604" t="n">
-        <v>24.92000007629395</v>
+        <v>25.10000038146973</v>
       </c>
       <c r="C4604" t="n">
-        <v>25.3799991607666</v>
+        <v>25.36000061035156</v>
       </c>
       <c r="D4604" t="n">
-        <v>24.8799991607666</v>
+        <v>24.77000045776367</v>
       </c>
       <c r="E4604" t="n">
-        <v>24.89999961853027</v>
+        <v>25.1299991607666</v>
       </c>
       <c r="F4604" t="n">
-        <v>7580500</v>
+        <v>13455000</v>
       </c>
     </row>
     <row r="4605">
       <c r="A4605" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B4605" t="n">
+        <v>24.92000007629395</v>
+      </c>
+      <c r="C4605" t="n">
+        <v>25.3799991607666</v>
+      </c>
+      <c r="D4605" t="n">
+        <v>24.8799991607666</v>
+      </c>
+      <c r="E4605" t="n">
+        <v>24.89999961853027</v>
+      </c>
+      <c r="F4605" t="n">
+        <v>7580500</v>
+      </c>
+    </row>
+    <row r="4606">
+      <c r="A4606" s="1" t="n">
         <v>46255</v>
       </c>
-      <c r="B4605" t="n">
-        <v>25.36</v>
-      </c>
-      <c r="C4605" t="n">
-        <v>25.62</v>
-      </c>
-      <c r="D4605" t="n">
-        <v>24.93</v>
-      </c>
-      <c r="E4605" t="n">
-        <v>25.12</v>
-      </c>
-      <c r="F4605" t="n">
+      <c r="B4606" t="n">
+        <v>25.36000061035156</v>
+      </c>
+      <c r="C4606" t="n">
+        <v>25.6200008392334</v>
+      </c>
+      <c r="D4606" t="n">
+        <v>24.93000030517578</v>
+      </c>
+      <c r="E4606" t="n">
+        <v>25.1200008392334</v>
+      </c>
+      <c r="F4606" t="n">
         <v>27481200</v>
+      </c>
+    </row>
+    <row r="4607">
+      <c r="A4607" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B4607" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="C4607" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="D4607" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4607" t="n">
+        <v>25</v>
+      </c>
+      <c r="F4607" t="n">
+        <v>9025500</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4607"/>
+  <dimension ref="A1:F4608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92552,10 +92552,10 @@
         <v>46258</v>
       </c>
       <c r="B4607" t="n">
-        <v>26.1</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="C4607" t="n">
-        <v>26.36</v>
+        <v>26.36000061035156</v>
       </c>
       <c r="D4607" t="n">
         <v>25</v>
@@ -92565,6 +92565,26 @@
       </c>
       <c r="F4607" t="n">
         <v>9025500</v>
+      </c>
+    </row>
+    <row r="4608">
+      <c r="A4608" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B4608" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="C4608" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="D4608" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="E4608" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="F4608" t="n">
+        <v>13966000</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4608"/>
+  <dimension ref="A1:F4609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92572,19 +92572,39 @@
         <v>46259</v>
       </c>
       <c r="B4608" t="n">
-        <v>26.69</v>
+        <v>26.69000053405762</v>
       </c>
       <c r="C4608" t="n">
-        <v>26.83</v>
+        <v>26.82999992370605</v>
       </c>
       <c r="D4608" t="n">
-        <v>26.08</v>
+        <v>26.07999992370605</v>
       </c>
       <c r="E4608" t="n">
-        <v>26.19</v>
+        <v>26.19000053405762</v>
       </c>
       <c r="F4608" t="n">
         <v>13966000</v>
+      </c>
+    </row>
+    <row r="4609">
+      <c r="A4609" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B4609" t="n">
+        <v>26.3799991607666</v>
+      </c>
+      <c r="C4609" t="n">
+        <v>26.95000076293945</v>
+      </c>
+      <c r="D4609" t="n">
+        <v>26.20999908447266</v>
+      </c>
+      <c r="E4609" t="n">
+        <v>26.65999984741211</v>
+      </c>
+      <c r="F4609" t="n">
+        <v>13134400</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -92349,262 +92349,262 @@
     </row>
     <row r="4597">
       <c r="A4597" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B4597" t="n">
-        <v>25.31999969482422</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="C4597" t="n">
-        <v>26.14999961853027</v>
+        <v>25.38999938964844</v>
       </c>
       <c r="D4597" t="n">
-        <v>25.29999923706055</v>
+        <v>24.5</v>
       </c>
       <c r="E4597" t="n">
-        <v>25.95999908447266</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="F4597" t="n">
-        <v>11408000</v>
+        <v>12371700</v>
       </c>
     </row>
     <row r="4598">
       <c r="A4598" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B4598" t="n">
-        <v>24.54999923706055</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="C4598" t="n">
-        <v>25.38999938964844</v>
+        <v>24.63999938964844</v>
       </c>
       <c r="D4598" t="n">
-        <v>24.5</v>
+        <v>23.98999977111816</v>
       </c>
       <c r="E4598" t="n">
-        <v>25.20000076293945</v>
+        <v>24.54000091552734</v>
       </c>
       <c r="F4598" t="n">
-        <v>12371700</v>
+        <v>16842400</v>
       </c>
     </row>
     <row r="4599">
       <c r="A4599" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B4599" t="n">
+        <v>24.34000015258789</v>
+      </c>
+      <c r="C4599" t="n">
+        <v>24.71999931335449</v>
+      </c>
+      <c r="D4599" t="n">
+        <v>24.03000068664551</v>
+      </c>
+      <c r="E4599" t="n">
         <v>24.11000061035156</v>
       </c>
-      <c r="C4599" t="n">
-        <v>24.63999938964844</v>
-      </c>
-      <c r="D4599" t="n">
-        <v>23.98999977111816</v>
-      </c>
-      <c r="E4599" t="n">
-        <v>24.54000091552734</v>
-      </c>
       <c r="F4599" t="n">
-        <v>16842400</v>
+        <v>9052700</v>
       </c>
     </row>
     <row r="4600">
       <c r="A4600" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B4600" t="n">
-        <v>24.34000015258789</v>
+        <v>24.45000076293945</v>
       </c>
       <c r="C4600" t="n">
-        <v>24.71999931335449</v>
+        <v>24.61000061035156</v>
       </c>
       <c r="D4600" t="n">
-        <v>24.03000068664551</v>
+        <v>23.64999961853027</v>
       </c>
       <c r="E4600" t="n">
-        <v>24.11000061035156</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="F4600" t="n">
-        <v>9052700</v>
+        <v>13652000</v>
       </c>
     </row>
     <row r="4601">
       <c r="A4601" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B4601" t="n">
-        <v>24.45000076293945</v>
+        <v>24.53000068664551</v>
       </c>
       <c r="C4601" t="n">
-        <v>24.61000061035156</v>
+        <v>24.8700008392334</v>
       </c>
       <c r="D4601" t="n">
-        <v>23.64999961853027</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="E4601" t="n">
-        <v>24.20000076293945</v>
+        <v>24.3799991607666</v>
       </c>
       <c r="F4601" t="n">
-        <v>13652000</v>
+        <v>12423700</v>
       </c>
     </row>
     <row r="4602">
       <c r="A4602" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B4602" t="n">
-        <v>24.53000068664551</v>
+        <v>24.64999961853027</v>
       </c>
       <c r="C4602" t="n">
-        <v>24.8700008392334</v>
+        <v>24.90999984741211</v>
       </c>
       <c r="D4602" t="n">
-        <v>24.20000076293945</v>
+        <v>24.35000038146973</v>
       </c>
       <c r="E4602" t="n">
-        <v>24.3799991607666</v>
+        <v>24.47999954223633</v>
       </c>
       <c r="F4602" t="n">
-        <v>12423700</v>
+        <v>6850200</v>
       </c>
     </row>
     <row r="4603">
       <c r="A4603" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B4603" t="n">
-        <v>24.64999961853027</v>
+        <v>25.10000038146973</v>
       </c>
       <c r="C4603" t="n">
-        <v>24.90999984741211</v>
+        <v>25.36000061035156</v>
       </c>
       <c r="D4603" t="n">
-        <v>24.35000038146973</v>
+        <v>24.77000045776367</v>
       </c>
       <c r="E4603" t="n">
-        <v>24.47999954223633</v>
+        <v>25.1299991607666</v>
       </c>
       <c r="F4603" t="n">
-        <v>6850200</v>
+        <v>13455000</v>
       </c>
     </row>
     <row r="4604">
       <c r="A4604" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B4604" t="n">
-        <v>25.10000038146973</v>
+        <v>24.92000007629395</v>
       </c>
       <c r="C4604" t="n">
-        <v>25.36000061035156</v>
+        <v>25.3799991607666</v>
       </c>
       <c r="D4604" t="n">
-        <v>24.77000045776367</v>
+        <v>24.8799991607666</v>
       </c>
       <c r="E4604" t="n">
-        <v>25.1299991607666</v>
+        <v>24.89999961853027</v>
       </c>
       <c r="F4604" t="n">
-        <v>13455000</v>
+        <v>7580500</v>
       </c>
     </row>
     <row r="4605">
       <c r="A4605" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B4605" t="n">
-        <v>24.92000007629395</v>
+        <v>25.36000061035156</v>
       </c>
       <c r="C4605" t="n">
-        <v>25.3799991607666</v>
+        <v>25.6200008392334</v>
       </c>
       <c r="D4605" t="n">
-        <v>24.8799991607666</v>
+        <v>24.93000030517578</v>
       </c>
       <c r="E4605" t="n">
-        <v>24.89999961853027</v>
+        <v>25.1200008392334</v>
       </c>
       <c r="F4605" t="n">
-        <v>7580500</v>
+        <v>27481200</v>
       </c>
     </row>
     <row r="4606">
       <c r="A4606" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B4606" t="n">
-        <v>25.36000061035156</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="C4606" t="n">
-        <v>25.6200008392334</v>
+        <v>26.36000061035156</v>
       </c>
       <c r="D4606" t="n">
-        <v>24.93000030517578</v>
+        <v>25</v>
       </c>
       <c r="E4606" t="n">
-        <v>25.1200008392334</v>
+        <v>25</v>
       </c>
       <c r="F4606" t="n">
-        <v>27481200</v>
+        <v>9025500</v>
       </c>
     </row>
     <row r="4607">
       <c r="A4607" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B4607" t="n">
-        <v>26.10000038146973</v>
+        <v>26.69000053405762</v>
       </c>
       <c r="C4607" t="n">
-        <v>26.36000061035156</v>
+        <v>26.82999992370605</v>
       </c>
       <c r="D4607" t="n">
-        <v>25</v>
+        <v>26.07999992370605</v>
       </c>
       <c r="E4607" t="n">
-        <v>25</v>
+        <v>26.19000053405762</v>
       </c>
       <c r="F4607" t="n">
-        <v>9025500</v>
+        <v>13966000</v>
       </c>
     </row>
     <row r="4608">
       <c r="A4608" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B4608" t="n">
-        <v>26.69000053405762</v>
+        <v>26.3799991607666</v>
       </c>
       <c r="C4608" t="n">
-        <v>26.82999992370605</v>
+        <v>26.95000076293945</v>
       </c>
       <c r="D4608" t="n">
-        <v>26.07999992370605</v>
+        <v>26.20999908447266</v>
       </c>
       <c r="E4608" t="n">
-        <v>26.19000053405762</v>
+        <v>26.65999984741211</v>
       </c>
       <c r="F4608" t="n">
-        <v>13966000</v>
+        <v>13139300</v>
       </c>
     </row>
     <row r="4609">
       <c r="A4609" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B4609" t="n">
-        <v>26.3799991607666</v>
+        <v>26.15</v>
       </c>
       <c r="C4609" t="n">
-        <v>26.95000076293945</v>
+        <v>26.54</v>
       </c>
       <c r="D4609" t="n">
-        <v>26.20999908447266</v>
+        <v>26.03</v>
       </c>
       <c r="E4609" t="n">
-        <v>26.65999984741211</v>
+        <v>26.03</v>
       </c>
       <c r="F4609" t="n">
-        <v>13134400</v>
+        <v>10352000</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4609"/>
+  <dimension ref="A1:F4611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92349,262 +92349,302 @@
     </row>
     <row r="4597">
       <c r="A4597" s="1" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B4597" t="n">
-        <v>24.54999923706055</v>
+        <v>25.31999969482422</v>
       </c>
       <c r="C4597" t="n">
-        <v>25.38999938964844</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="D4597" t="n">
-        <v>24.5</v>
+        <v>25.29999923706055</v>
       </c>
       <c r="E4597" t="n">
-        <v>25.20000076293945</v>
+        <v>25.95999908447266</v>
       </c>
       <c r="F4597" t="n">
-        <v>12371700</v>
+        <v>11408000</v>
       </c>
     </row>
     <row r="4598">
       <c r="A4598" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B4598" t="n">
-        <v>24.11000061035156</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="C4598" t="n">
-        <v>24.63999938964844</v>
+        <v>25.38999938964844</v>
       </c>
       <c r="D4598" t="n">
-        <v>23.98999977111816</v>
+        <v>24.5</v>
       </c>
       <c r="E4598" t="n">
-        <v>24.54000091552734</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="F4598" t="n">
-        <v>16842400</v>
+        <v>12371700</v>
       </c>
     </row>
     <row r="4599">
       <c r="A4599" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B4599" t="n">
-        <v>24.34000015258789</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="C4599" t="n">
-        <v>24.71999931335449</v>
+        <v>24.63999938964844</v>
       </c>
       <c r="D4599" t="n">
-        <v>24.03000068664551</v>
+        <v>23.98999977111816</v>
       </c>
       <c r="E4599" t="n">
-        <v>24.11000061035156</v>
+        <v>24.54000091552734</v>
       </c>
       <c r="F4599" t="n">
-        <v>9052700</v>
+        <v>16842400</v>
       </c>
     </row>
     <row r="4600">
       <c r="A4600" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B4600" t="n">
-        <v>24.45000076293945</v>
+        <v>24.34000015258789</v>
       </c>
       <c r="C4600" t="n">
-        <v>24.61000061035156</v>
+        <v>24.71999931335449</v>
       </c>
       <c r="D4600" t="n">
-        <v>23.64999961853027</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="E4600" t="n">
-        <v>24.20000076293945</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="F4600" t="n">
-        <v>13652000</v>
+        <v>9052700</v>
       </c>
     </row>
     <row r="4601">
       <c r="A4601" s="1" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B4601" t="n">
-        <v>24.53000068664551</v>
+        <v>24.45000076293945</v>
       </c>
       <c r="C4601" t="n">
-        <v>24.8700008392334</v>
+        <v>24.61000061035156</v>
       </c>
       <c r="D4601" t="n">
+        <v>23.64999961853027</v>
+      </c>
+      <c r="E4601" t="n">
         <v>24.20000076293945</v>
       </c>
-      <c r="E4601" t="n">
-        <v>24.3799991607666</v>
-      </c>
       <c r="F4601" t="n">
-        <v>12423700</v>
+        <v>13652000</v>
       </c>
     </row>
     <row r="4602">
       <c r="A4602" s="1" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B4602" t="n">
-        <v>24.64999961853027</v>
+        <v>24.53000068664551</v>
       </c>
       <c r="C4602" t="n">
-        <v>24.90999984741211</v>
+        <v>24.8700008392334</v>
       </c>
       <c r="D4602" t="n">
-        <v>24.35000038146973</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="E4602" t="n">
-        <v>24.47999954223633</v>
+        <v>24.3799991607666</v>
       </c>
       <c r="F4602" t="n">
-        <v>6850200</v>
+        <v>12423700</v>
       </c>
     </row>
     <row r="4603">
       <c r="A4603" s="1" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B4603" t="n">
-        <v>25.10000038146973</v>
+        <v>24.64999961853027</v>
       </c>
       <c r="C4603" t="n">
-        <v>25.36000061035156</v>
+        <v>24.90999984741211</v>
       </c>
       <c r="D4603" t="n">
-        <v>24.77000045776367</v>
+        <v>24.35000038146973</v>
       </c>
       <c r="E4603" t="n">
-        <v>25.1299991607666</v>
+        <v>24.47999954223633</v>
       </c>
       <c r="F4603" t="n">
-        <v>13455000</v>
+        <v>6850200</v>
       </c>
     </row>
     <row r="4604">
       <c r="A4604" s="1" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B4604" t="n">
-        <v>24.92000007629395</v>
+        <v>25.10000038146973</v>
       </c>
       <c r="C4604" t="n">
-        <v>25.3799991607666</v>
+        <v>25.36000061035156</v>
       </c>
       <c r="D4604" t="n">
-        <v>24.8799991607666</v>
+        <v>24.77000045776367</v>
       </c>
       <c r="E4604" t="n">
-        <v>24.89999961853027</v>
+        <v>25.1299991607666</v>
       </c>
       <c r="F4604" t="n">
-        <v>7580500</v>
+        <v>13455000</v>
       </c>
     </row>
     <row r="4605">
       <c r="A4605" s="1" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B4605" t="n">
-        <v>25.36000061035156</v>
+        <v>24.92000007629395</v>
       </c>
       <c r="C4605" t="n">
-        <v>25.6200008392334</v>
+        <v>25.3799991607666</v>
       </c>
       <c r="D4605" t="n">
-        <v>24.93000030517578</v>
+        <v>24.8799991607666</v>
       </c>
       <c r="E4605" t="n">
-        <v>25.1200008392334</v>
+        <v>24.89999961853027</v>
       </c>
       <c r="F4605" t="n">
-        <v>27481200</v>
+        <v>7580500</v>
       </c>
     </row>
     <row r="4606">
       <c r="A4606" s="1" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B4606" t="n">
-        <v>26.10000038146973</v>
+        <v>25.36000061035156</v>
       </c>
       <c r="C4606" t="n">
-        <v>26.36000061035156</v>
+        <v>25.6200008392334</v>
       </c>
       <c r="D4606" t="n">
-        <v>25</v>
+        <v>24.93000030517578</v>
       </c>
       <c r="E4606" t="n">
-        <v>25</v>
+        <v>25.1200008392334</v>
       </c>
       <c r="F4606" t="n">
-        <v>9025500</v>
+        <v>27481200</v>
       </c>
     </row>
     <row r="4607">
       <c r="A4607" s="1" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B4607" t="n">
-        <v>26.69000053405762</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="C4607" t="n">
-        <v>26.82999992370605</v>
+        <v>26.36000061035156</v>
       </c>
       <c r="D4607" t="n">
-        <v>26.07999992370605</v>
+        <v>25</v>
       </c>
       <c r="E4607" t="n">
-        <v>26.19000053405762</v>
+        <v>25</v>
       </c>
       <c r="F4607" t="n">
-        <v>13966000</v>
+        <v>9025500</v>
       </c>
     </row>
     <row r="4608">
       <c r="A4608" s="1" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B4608" t="n">
-        <v>26.3799991607666</v>
+        <v>26.69000053405762</v>
       </c>
       <c r="C4608" t="n">
-        <v>26.95000076293945</v>
+        <v>26.82999992370605</v>
       </c>
       <c r="D4608" t="n">
-        <v>26.20999908447266</v>
+        <v>26.07999992370605</v>
       </c>
       <c r="E4608" t="n">
-        <v>26.65999984741211</v>
+        <v>26.19000053405762</v>
       </c>
       <c r="F4608" t="n">
-        <v>13139300</v>
+        <v>13966000</v>
       </c>
     </row>
     <row r="4609">
       <c r="A4609" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B4609" t="n">
+        <v>26.3799991607666</v>
+      </c>
+      <c r="C4609" t="n">
+        <v>26.95000076293945</v>
+      </c>
+      <c r="D4609" t="n">
+        <v>26.20999908447266</v>
+      </c>
+      <c r="E4609" t="n">
+        <v>26.65999984741211</v>
+      </c>
+      <c r="F4609" t="n">
+        <v>13139300</v>
+      </c>
+    </row>
+    <row r="4610">
+      <c r="A4610" s="1" t="n">
         <v>46261</v>
       </c>
-      <c r="B4609" t="n">
-        <v>26.15</v>
-      </c>
-      <c r="C4609" t="n">
-        <v>26.54</v>
-      </c>
-      <c r="D4609" t="n">
-        <v>26.03</v>
-      </c>
-      <c r="E4609" t="n">
-        <v>26.03</v>
-      </c>
-      <c r="F4609" t="n">
+      <c r="B4610" t="n">
+        <v>26.14999961853027</v>
+      </c>
+      <c r="C4610" t="n">
+        <v>26.54000091552734</v>
+      </c>
+      <c r="D4610" t="n">
+        <v>26.03000068664551</v>
+      </c>
+      <c r="E4610" t="n">
+        <v>26.03000068664551</v>
+      </c>
+      <c r="F4610" t="n">
         <v>10352000</v>
+      </c>
+    </row>
+    <row r="4611">
+      <c r="A4611" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B4611" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="C4611" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="D4611" t="n">
+        <v>26</v>
+      </c>
+      <c r="E4611" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="F4611" t="n">
+        <v>7198100</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -92632,7 +92632,7 @@
         <v>46262</v>
       </c>
       <c r="B4611" t="n">
-        <v>26.28</v>
+        <v>26.3</v>
       </c>
       <c r="C4611" t="n">
         <v>26.52</v>
@@ -92644,7 +92644,7 @@
         <v>26.35</v>
       </c>
       <c r="F4611" t="n">
-        <v>7198100</v>
+        <v>10760200</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -92631,18 +92631,10 @@
       <c r="A4611" s="1" t="n">
         <v>46262</v>
       </c>
-      <c r="B4611" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="C4611" t="n">
-        <v>26.52</v>
-      </c>
-      <c r="D4611" t="n">
-        <v>26</v>
-      </c>
-      <c r="E4611" t="n">
-        <v>26.35</v>
-      </c>
+      <c r="B4611" t="inlineStr"/>
+      <c r="C4611" t="inlineStr"/>
+      <c r="D4611" t="inlineStr"/>
+      <c r="E4611" t="inlineStr"/>
       <c r="F4611" t="n">
         <v>10760200</v>
       </c>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4611"/>
+  <dimension ref="A1:F4613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92631,12 +92631,60 @@
       <c r="A4611" s="1" t="n">
         <v>46262</v>
       </c>
-      <c r="B4611" t="inlineStr"/>
-      <c r="C4611" t="inlineStr"/>
-      <c r="D4611" t="inlineStr"/>
-      <c r="E4611" t="inlineStr"/>
+      <c r="B4611" t="n">
+        <v>26.29999923706055</v>
+      </c>
+      <c r="C4611" t="n">
+        <v>26.52000045776367</v>
+      </c>
+      <c r="D4611" t="n">
+        <v>26</v>
+      </c>
+      <c r="E4611" t="n">
+        <v>26.35000038146973</v>
+      </c>
       <c r="F4611" t="n">
-        <v>10760200</v>
+        <v>10765400</v>
+      </c>
+    </row>
+    <row r="4612">
+      <c r="A4612" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B4612" t="n">
+        <v>26.20999908447266</v>
+      </c>
+      <c r="C4612" t="n">
+        <v>26.85000038146973</v>
+      </c>
+      <c r="D4612" t="n">
+        <v>26.1200008392334</v>
+      </c>
+      <c r="E4612" t="n">
+        <v>26.54000091552734</v>
+      </c>
+      <c r="F4612" t="n">
+        <v>9349200</v>
+      </c>
+    </row>
+    <row r="4613">
+      <c r="A4613" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B4613" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="C4613" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="D4613" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="E4613" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="F4613" t="n">
+        <v>16752300</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4613"/>
+  <dimension ref="A1:F4614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92672,19 +92672,39 @@
         <v>46266</v>
       </c>
       <c r="B4613" t="n">
-        <v>26.52</v>
+        <v>26.52000045776367</v>
       </c>
       <c r="C4613" t="n">
-        <v>26.93</v>
+        <v>26.93000030517578</v>
       </c>
       <c r="D4613" t="n">
-        <v>26.09</v>
+        <v>26.09000015258789</v>
       </c>
       <c r="E4613" t="n">
-        <v>26.48</v>
+        <v>26.47999954223633</v>
       </c>
       <c r="F4613" t="n">
         <v>16752300</v>
+      </c>
+    </row>
+    <row r="4614">
+      <c r="A4614" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B4614" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="C4614" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="D4614" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="E4614" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4614" t="n">
+        <v>20531800</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4614"/>
+  <dimension ref="A1:F4615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92692,19 +92692,39 @@
         <v>46267</v>
       </c>
       <c r="B4614" t="n">
-        <v>27.43</v>
+        <v>27.43000030517578</v>
       </c>
       <c r="C4614" t="n">
-        <v>27.96</v>
+        <v>27.95999908447266</v>
       </c>
       <c r="D4614" t="n">
-        <v>26.91</v>
+        <v>26.90999984741211</v>
       </c>
       <c r="E4614" t="n">
         <v>27</v>
       </c>
       <c r="F4614" t="n">
         <v>20531800</v>
+      </c>
+    </row>
+    <row r="4615">
+      <c r="A4615" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B4615" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="C4615" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="D4615" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="E4615" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="F4615" t="n">
+        <v>11561000</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4615"/>
+  <dimension ref="A1:F4616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92712,19 +92712,39 @@
         <v>46268</v>
       </c>
       <c r="B4615" t="n">
-        <v>27.64</v>
+        <v>27.63999938964844</v>
       </c>
       <c r="C4615" t="n">
-        <v>27.94</v>
+        <v>27.94000053405762</v>
       </c>
       <c r="D4615" t="n">
-        <v>27.48</v>
+        <v>27.47999954223633</v>
       </c>
       <c r="E4615" t="n">
-        <v>27.88</v>
+        <v>27.8799991607666</v>
       </c>
       <c r="F4615" t="n">
         <v>11561000</v>
+      </c>
+    </row>
+    <row r="4616">
+      <c r="A4616" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B4616" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="C4616" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="D4616" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E4616" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="F4616" t="n">
+        <v>5839700</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -92732,16 +92732,16 @@
         <v>46269</v>
       </c>
       <c r="B4616" t="n">
-        <v>27.59</v>
+        <v>27.59000015258789</v>
       </c>
       <c r="C4616" t="n">
-        <v>27.84</v>
+        <v>27.84000015258789</v>
       </c>
       <c r="D4616" t="n">
-        <v>27.2</v>
+        <v>27.20000076293945</v>
       </c>
       <c r="E4616" t="n">
-        <v>27.67</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="F4616" t="n">
         <v>5839700</v>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4616"/>
+  <dimension ref="A1:F4617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92747,6 +92747,26 @@
         <v>5839700</v>
       </c>
     </row>
+    <row r="4617">
+      <c r="A4617" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B4617" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="C4617" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="D4617" t="n">
+        <v>27.61</v>
+      </c>
+      <c r="E4617" t="n">
+        <v>28</v>
+      </c>
+      <c r="F4617" t="n">
+        <v>9551500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4617"/>
+  <dimension ref="A1:F4618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92752,19 +92752,39 @@
         <v>46273</v>
       </c>
       <c r="B4617" t="n">
-        <v>27.69</v>
+        <v>27.69000053405762</v>
       </c>
       <c r="C4617" t="n">
-        <v>28.15</v>
+        <v>28.14999961853027</v>
       </c>
       <c r="D4617" t="n">
-        <v>27.61</v>
+        <v>27.61000061035156</v>
       </c>
       <c r="E4617" t="n">
         <v>28</v>
       </c>
       <c r="F4617" t="n">
         <v>9551500</v>
+      </c>
+    </row>
+    <row r="4618">
+      <c r="A4618" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B4618" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="C4618" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D4618" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="E4618" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F4618" t="n">
+        <v>5732700</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4618"/>
+  <dimension ref="A1:F4619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92772,19 +92772,39 @@
         <v>46274</v>
       </c>
       <c r="B4618" t="n">
-        <v>27.33</v>
+        <v>27.32999992370605</v>
       </c>
       <c r="C4618" t="n">
-        <v>27.6</v>
+        <v>27.60000038146973</v>
       </c>
       <c r="D4618" t="n">
-        <v>27.06</v>
+        <v>27.05999946594238</v>
       </c>
       <c r="E4618" t="n">
         <v>27.5</v>
       </c>
       <c r="F4618" t="n">
         <v>5732700</v>
+      </c>
+    </row>
+    <row r="4619">
+      <c r="A4619" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B4619" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="C4619" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="D4619" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="E4619" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="F4619" t="n">
+        <v>10140800</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4619"/>
+  <dimension ref="A1:F4620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92792,19 +92792,39 @@
         <v>46275</v>
       </c>
       <c r="B4619" t="n">
-        <v>27.68</v>
+        <v>27.68000030517578</v>
       </c>
       <c r="C4619" t="n">
-        <v>27.82</v>
+        <v>27.81999969482422</v>
       </c>
       <c r="D4619" t="n">
-        <v>27.07</v>
+        <v>27.06999969482422</v>
       </c>
       <c r="E4619" t="n">
-        <v>27.45</v>
+        <v>27.45000076293945</v>
       </c>
       <c r="F4619" t="n">
-        <v>10140800</v>
+        <v>10160000</v>
+      </c>
+    </row>
+    <row r="4620">
+      <c r="A4620" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B4620" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="C4620" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="D4620" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="E4620" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="F4620" t="n">
+        <v>5936800</v>
       </c>
     </row>
   </sheetData>
